--- a/R8_県学調_問題マスタ.xlsx
+++ b/R8_県学調_問題マスタ.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9149d06814ece6b4/github/survey-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{14723A84-59D9-41EF-B850-FD79EA8212AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CF9C1E1-C317-42E7-A42F-80C9BE653CA1}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{14723A84-59D9-41EF-B850-FD79EA8212AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93FE0F33-093A-4B05-BCA0-A5E5017E3E65}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="問題マスタ" sheetId="6" r:id="rId1"/>
-    <sheet name="小学校コード一覧表" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="中学校コード一覧表" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="選択肢マスタ" sheetId="7" r:id="rId2"/>
+    <sheet name="小学校コード一覧表" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="中学校コード一覧表" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">小学校コード一覧表!$A$2:$D$318</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">小学校コード一覧表!$A$1:$E$318</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">中学校コード一覧表!$A$1:$E$202</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">小学校コード一覧表!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">中学校コード一覧表!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">小学校コード一覧表!$A$2:$D$318</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">小学校コード一覧表!$A$1:$E$318</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">中学校コード一覧表!$A$1:$E$202</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">小学校コード一覧表!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">中学校コード一覧表!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="714">
   <si>
     <t>学校コード一覧表</t>
     <rPh sb="0" eb="2">
@@ -2886,6 +2887,108 @@
     <rPh sb="0" eb="4">
       <t>ニュウリョクウム</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題番号</t>
+  </si>
+  <si>
+    <t>CSV項目キー</t>
+  </si>
+  <si>
+    <t>CSV項目出現順</t>
+  </si>
+  <si>
+    <t>RESPONSEキー</t>
+  </si>
+  <si>
+    <t>回答値</t>
+  </si>
+  <si>
+    <t>表示値</t>
+  </si>
+  <si>
+    <t>表示順</t>
+  </si>
+  <si>
+    <t>111_R7県学調_小_国1-1   </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正答フラグ</t>
+  </si>
+  <si>
+    <t>111_R7県学調_小_国1-1</t>
+  </si>
+  <si>
+    <t>choice_1</t>
+  </si>
+  <si>
+    <t>１　自分が考えたことについて、ほかの人に、どう思うかを問いかけている。</t>
+  </si>
+  <si>
+    <t>choice_2</t>
+  </si>
+  <si>
+    <t>２　自分の考えを分かりやすく伝えるために、自分が体験したことを挙げている。</t>
+  </si>
+  <si>
+    <t>choice_3</t>
+  </si>
+  <si>
+    <t>３　アンケートの結果から読み取ったことをもとに、自分の考えを話している。</t>
+  </si>
+  <si>
+    <t>４　アンケート結果の中でぎもんに思ったことを、ほかの人にたずねている。</t>
+  </si>
+  <si>
+    <t>RESPONSE</t>
+  </si>
+  <si>
+    <t>choice_5</t>
+  </si>
+  <si>
+    <t>choice_6</t>
+  </si>
+  <si>
+    <t>choice_7</t>
+  </si>
+  <si>
+    <t>222_R7県学調_小_算2-2-1</t>
+  </si>
+  <si>
+    <t>QTIのchoice_1→CSVのchoice_5として読替</t>
+  </si>
+  <si>
+    <t>QTIのchoice_2→CSVのchoice_6として読替</t>
+  </si>
+  <si>
+    <t>QTIのchoice_3→CSVのchoice_7として読替（正答）</t>
+  </si>
+  <si>
+    <t>choice_8</t>
+  </si>
+  <si>
+    <t>QTIのchoice_4→CSVのchoice_8として読替</t>
+  </si>
+  <si>
+    <t>①　フランスパン</t>
+  </si>
+  <si>
+    <t>QTIどおり</t>
+  </si>
+  <si>
+    <t>②　食パン</t>
+  </si>
+  <si>
+    <t>③　どちらも同じ</t>
+  </si>
+  <si>
+    <t>Q1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q5</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4000,6 +4103,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{745149EE-5328-49D7-8122-57D6B21A8DDE}" name="テーブル3" displayName="テーブル3" ref="A1:I22" totalsRowShown="0">
+  <autoFilter ref="A1:I22" xr:uid="{745149EE-5328-49D7-8122-57D6B21A8DDE}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{830376B8-C46D-4951-8DB7-1156BA4B22B4}" name="問題番号"/>
+    <tableColumn id="2" xr3:uid="{4F9B421B-F66F-44C5-8C74-A6ACACF219FF}" name="CSV項目キー"/>
+    <tableColumn id="3" xr3:uid="{98AC1322-6957-464D-9F03-7D07FD73688C}" name="CSV項目出現順"/>
+    <tableColumn id="4" xr3:uid="{C7D2F86E-86CB-4D30-B79D-2A2288CEF0C6}" name="RESPONSEキー"/>
+    <tableColumn id="5" xr3:uid="{E21108EB-638E-4268-ADAD-6851C885FCC7}" name="回答値"/>
+    <tableColumn id="6" xr3:uid="{B112ECCE-1452-4DCA-910E-1FE348BE910F}" name="表示値"/>
+    <tableColumn id="7" xr3:uid="{24E76348-58F9-4CE6-9C38-8C034E214EB1}" name="表示順"/>
+    <tableColumn id="8" xr3:uid="{9855A2A8-1152-4174-B384-4592458FE6F3}" name="正答フラグ"/>
+    <tableColumn id="9" xr3:uid="{A2B3798D-5E58-44C6-8D0C-8E5C822D6370}" name="備考"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BAA040B5-8ED9-4622-B97A-11270A60D126}" name="_tablesho" displayName="_tablesho" ref="A2:D318" totalsRowShown="0" tableBorderDxfId="9">
   <autoFilter ref="A2:D318" xr:uid="{BAA040B5-8ED9-4622-B97A-11270A60D126}"/>
   <tableColumns count="4">
@@ -4012,7 +4133,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9B11CD57-71E2-4773-9D23-F8794F6BC098}" name="_tablechu" displayName="_tablechu" ref="A2:D202" totalsRowShown="0" tableBorderDxfId="4">
   <autoFilter ref="A2:D202" xr:uid="{9B11CD57-71E2-4773-9D23-F8794F6BC098}"/>
   <tableColumns count="4">
@@ -4289,20 +4410,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731ACD8B-3F3F-4FB8-AC79-3009D1AB82F2}">
   <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="2" max="3" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.25" customWidth="1"/>
+    <col min="2" max="3" width="10.2109375" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.2109375" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.875" customWidth="1"/>
-    <col min="12" max="12" width="19.875" customWidth="1"/>
-    <col min="13" max="13" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="10.25" customWidth="1"/>
+    <col min="10" max="11" width="16.85546875" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.2109375" customWidth="1"/>
+    <col min="16" max="16" width="10.2109375" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>655</v>
       </c>
@@ -4361,7 +4482,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>566</v>
       </c>
@@ -4387,7 +4508,7 @@
         <v>571</v>
       </c>
       <c r="I2" t="s">
-        <v>572</v>
+        <v>688</v>
       </c>
       <c r="J2" t="s">
         <v>566</v>
@@ -4417,7 +4538,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>580</v>
       </c>
@@ -4473,7 +4594,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>588</v>
       </c>
@@ -4529,7 +4650,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>596</v>
       </c>
@@ -4585,7 +4706,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>601</v>
       </c>
@@ -4641,7 +4762,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>608</v>
       </c>
@@ -4694,7 +4815,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>613</v>
       </c>
@@ -4747,7 +4868,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>619</v>
       </c>
@@ -4803,7 +4924,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>625</v>
       </c>
@@ -4859,7 +4980,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>630</v>
       </c>
@@ -4912,7 +5033,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A12" t="s">
         <v>636</v>
       </c>
@@ -4968,7 +5089,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A13" t="s">
         <v>646</v>
       </c>
@@ -5024,7 +5145,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A14" t="s">
         <v>650</v>
       </c>
@@ -5080,7 +5201,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A15" t="s">
         <v>654</v>
       </c>
@@ -5095,23 +5216,277 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33C08DAF-9E90-4F71-B777-114760BC3106}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
+  <cols>
+    <col min="1" max="1" width="9.92578125" customWidth="1"/>
+    <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.640625" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="9" max="9" width="51.92578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B1" t="s">
+        <v>682</v>
+      </c>
+      <c r="C1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D1" t="s">
+        <v>684</v>
+      </c>
+      <c r="E1" t="s">
+        <v>685</v>
+      </c>
+      <c r="F1" t="s">
+        <v>686</v>
+      </c>
+      <c r="G1" t="s">
+        <v>687</v>
+      </c>
+      <c r="H1" t="s">
+        <v>689</v>
+      </c>
+      <c r="I1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>678</v>
+      </c>
+      <c r="E2" t="s">
+        <v>699</v>
+      </c>
+      <c r="F2" t="s">
+        <v>692</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A3" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" t="s">
+        <v>690</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>678</v>
+      </c>
+      <c r="E3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F3" t="s">
+        <v>694</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A4" t="s">
+        <v>712</v>
+      </c>
+      <c r="B4" t="s">
+        <v>690</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>678</v>
+      </c>
+      <c r="E4" t="s">
+        <v>701</v>
+      </c>
+      <c r="F4" t="s">
+        <v>696</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A5" t="s">
+        <v>712</v>
+      </c>
+      <c r="B5" t="s">
+        <v>690</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>678</v>
+      </c>
+      <c r="E5" t="s">
+        <v>706</v>
+      </c>
+      <c r="F5" t="s">
+        <v>697</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B6" t="s">
+        <v>702</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>698</v>
+      </c>
+      <c r="E6" t="s">
+        <v>691</v>
+      </c>
+      <c r="F6" t="s">
+        <v>708</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A7" t="s">
+        <v>713</v>
+      </c>
+      <c r="B7" t="s">
+        <v>702</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>698</v>
+      </c>
+      <c r="E7" t="s">
+        <v>693</v>
+      </c>
+      <c r="F7" t="s">
+        <v>710</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="A8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B8" t="s">
+        <v>702</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>698</v>
+      </c>
+      <c r="E8" t="s">
+        <v>695</v>
+      </c>
+      <c r="F8" t="s">
+        <v>711</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>709</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FC969D-9D58-4E43-BD3E-79A846E161EE}">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I318"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="22.2109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5120,7 +5495,7 @@
       </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
@@ -5134,7 +5509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>110101</v>
       </c>
@@ -5148,7 +5523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>110102</v>
       </c>
@@ -5162,7 +5537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>110103</v>
       </c>
@@ -5176,7 +5551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>110104</v>
       </c>
@@ -5190,7 +5565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>110105</v>
       </c>
@@ -5204,7 +5579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>110106</v>
       </c>
@@ -5218,7 +5593,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>110107</v>
       </c>
@@ -5232,7 +5607,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>110108</v>
       </c>
@@ -5246,7 +5621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>110109</v>
       </c>
@@ -5260,7 +5635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>110110</v>
       </c>
@@ -5274,7 +5649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>110111</v>
       </c>
@@ -5288,7 +5663,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>110112</v>
       </c>
@@ -5302,7 +5677,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>110114</v>
       </c>
@@ -5316,7 +5691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>110115</v>
       </c>
@@ -5330,7 +5705,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>110116</v>
       </c>
@@ -5344,7 +5719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>110117</v>
       </c>
@@ -5358,7 +5733,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>110118</v>
       </c>
@@ -5372,7 +5747,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>110120</v>
       </c>
@@ -5386,7 +5761,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>110121</v>
       </c>
@@ -5400,7 +5775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>110122</v>
       </c>
@@ -5414,7 +5789,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>110124</v>
       </c>
@@ -5428,7 +5803,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>110125</v>
       </c>
@@ -5442,7 +5817,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>110126</v>
       </c>
@@ -5456,7 +5831,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>110127</v>
       </c>
@@ -5470,7 +5845,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>110128</v>
       </c>
@@ -5484,7 +5859,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>110129</v>
       </c>
@@ -5498,7 +5873,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>110130</v>
       </c>
@@ -5512,7 +5887,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>110131</v>
       </c>
@@ -5526,7 +5901,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>110132</v>
       </c>
@@ -5540,7 +5915,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>110133</v>
       </c>
@@ -5554,7 +5929,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>110134</v>
       </c>
@@ -5568,7 +5943,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>110135</v>
       </c>
@@ -5582,7 +5957,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>110136</v>
       </c>
@@ -5596,7 +5971,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>110137</v>
       </c>
@@ -5610,7 +5985,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>110138</v>
       </c>
@@ -5624,7 +5999,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>110139</v>
       </c>
@@ -5641,7 +6016,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>110140</v>
       </c>
@@ -5658,7 +6033,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>110143</v>
       </c>
@@ -5672,7 +6047,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>110145</v>
       </c>
@@ -5686,7 +6061,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>110146</v>
       </c>
@@ -5700,7 +6075,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>110201</v>
       </c>
@@ -5714,7 +6089,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>110202</v>
       </c>
@@ -5728,7 +6103,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>110204</v>
       </c>
@@ -5742,7 +6117,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>110301</v>
       </c>
@@ -5756,7 +6131,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>110302</v>
       </c>
@@ -5770,7 +6145,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>110304</v>
       </c>
@@ -5784,7 +6159,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>110306</v>
       </c>
@@ -5798,7 +6173,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>110308</v>
       </c>
@@ -5812,7 +6187,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>110401</v>
       </c>
@@ -5826,7 +6201,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>110402</v>
       </c>
@@ -5841,7 +6216,7 @@
       </c>
       <c r="I52" s="15"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>110404</v>
       </c>
@@ -5856,7 +6231,7 @@
       </c>
       <c r="I53" s="15"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>110405</v>
       </c>
@@ -5871,7 +6246,7 @@
       </c>
       <c r="I54" s="15"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>110501</v>
       </c>
@@ -5886,7 +6261,7 @@
       </c>
       <c r="I55" s="15"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>110502</v>
       </c>
@@ -5901,7 +6276,7 @@
       </c>
       <c r="I56" s="15"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>110503</v>
       </c>
@@ -5916,7 +6291,7 @@
       </c>
       <c r="I57" s="15"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>110504</v>
       </c>
@@ -5931,7 +6306,7 @@
       </c>
       <c r="I58" s="15"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>110505</v>
       </c>
@@ -5946,7 +6321,7 @@
       </c>
       <c r="I59" s="15"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>110506</v>
       </c>
@@ -5960,7 +6335,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>110507</v>
       </c>
@@ -5974,7 +6349,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>110508</v>
       </c>
@@ -5988,7 +6363,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>110509</v>
       </c>
@@ -6002,7 +6377,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <v>110601</v>
       </c>
@@ -6016,7 +6391,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="16">
         <v>110602</v>
       </c>
@@ -6030,7 +6405,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>110603</v>
       </c>
@@ -6044,7 +6419,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="16">
         <v>110604</v>
       </c>
@@ -6058,7 +6433,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>110607</v>
       </c>
@@ -6072,7 +6447,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>110701</v>
       </c>
@@ -6086,7 +6461,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>110702</v>
       </c>
@@ -6100,7 +6475,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>110703</v>
       </c>
@@ -6114,7 +6489,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>110704</v>
       </c>
@@ -6128,7 +6503,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>110801</v>
       </c>
@@ -6142,7 +6517,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>110802</v>
       </c>
@@ -6156,7 +6531,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>110803</v>
       </c>
@@ -6170,7 +6545,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>110804</v>
       </c>
@@ -6184,7 +6559,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>110805</v>
       </c>
@@ -6198,7 +6573,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>110806</v>
       </c>
@@ -6212,7 +6587,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>110807</v>
       </c>
@@ -6226,7 +6601,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <v>110808</v>
       </c>
@@ -6240,7 +6615,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>110809</v>
       </c>
@@ -6254,7 +6629,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="18">
         <v>110810</v>
       </c>
@@ -6268,7 +6643,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="16">
         <v>120901</v>
       </c>
@@ -6282,7 +6657,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>120902</v>
       </c>
@@ -6296,7 +6671,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>120903</v>
       </c>
@@ -6310,7 +6685,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>120904</v>
       </c>
@@ -6324,7 +6699,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>120905</v>
       </c>
@@ -6338,7 +6713,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>120906</v>
       </c>
@@ -6352,7 +6727,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>120907</v>
       </c>
@@ -6366,7 +6741,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>120908</v>
       </c>
@@ -6380,7 +6755,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>120909</v>
       </c>
@@ -6394,7 +6769,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
         <v>120910</v>
       </c>
@@ -6408,7 +6783,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <v>120912</v>
       </c>
@@ -6422,7 +6797,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
         <v>120915</v>
       </c>
@@ -6436,7 +6811,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
         <v>120916</v>
       </c>
@@ -6450,7 +6825,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
         <v>120917</v>
       </c>
@@ -6464,7 +6839,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
         <v>120918</v>
       </c>
@@ -6478,7 +6853,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
         <v>120919</v>
       </c>
@@ -6492,7 +6867,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
         <v>121001</v>
       </c>
@@ -6506,7 +6881,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
         <v>121002</v>
       </c>
@@ -6520,7 +6895,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
         <v>121003</v>
       </c>
@@ -6534,7 +6909,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
         <v>121004</v>
       </c>
@@ -6548,7 +6923,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
         <v>121005</v>
       </c>
@@ -6562,7 +6937,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
         <v>121006</v>
       </c>
@@ -6576,7 +6951,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
         <v>121007</v>
       </c>
@@ -6590,7 +6965,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
         <v>121008</v>
       </c>
@@ -6604,7 +6979,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
         <v>121009</v>
       </c>
@@ -6618,7 +6993,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
         <v>121010</v>
       </c>
@@ -6632,7 +7007,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
         <v>121011</v>
       </c>
@@ -6646,7 +7021,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
         <v>121101</v>
       </c>
@@ -6660,7 +7035,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
         <v>121102</v>
       </c>
@@ -6674,7 +7049,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="16">
         <v>121103</v>
       </c>
@@ -6688,7 +7063,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
         <v>121104</v>
       </c>
@@ -6702,7 +7077,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="16">
         <v>121105</v>
       </c>
@@ -6716,7 +7091,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
         <v>121106</v>
       </c>
@@ -6730,7 +7105,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="16">
         <v>121107</v>
       </c>
@@ -6744,7 +7119,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="16">
         <v>121111</v>
       </c>
@@ -6758,7 +7133,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
         <v>121112</v>
       </c>
@@ -6772,7 +7147,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="16">
         <v>121113</v>
       </c>
@@ -6786,7 +7161,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <v>121114</v>
       </c>
@@ -6800,7 +7175,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="16">
         <v>121115</v>
       </c>
@@ -6814,7 +7189,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
         <v>121116</v>
       </c>
@@ -6828,7 +7203,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="16">
         <v>121117</v>
       </c>
@@ -6842,7 +7217,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
         <v>121201</v>
       </c>
@@ -6856,7 +7231,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="18">
         <v>121202</v>
       </c>
@@ -6870,7 +7245,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="16">
         <v>121301</v>
       </c>
@@ -6884,7 +7259,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <v>121302</v>
       </c>
@@ -6898,7 +7273,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
         <v>121303</v>
       </c>
@@ -6912,7 +7287,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <v>121304</v>
       </c>
@@ -6926,7 +7301,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="16">
         <v>121305</v>
       </c>
@@ -6940,7 +7315,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <v>121306</v>
       </c>
@@ -6954,7 +7329,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
         <v>121307</v>
       </c>
@@ -6968,7 +7343,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <v>121309</v>
       </c>
@@ -6982,7 +7357,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
         <v>121310</v>
       </c>
@@ -6996,7 +7371,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <v>121311</v>
       </c>
@@ -7010,7 +7385,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
         <v>121317</v>
       </c>
@@ -7024,7 +7399,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <v>121320</v>
       </c>
@@ -7038,7 +7413,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
         <v>121321</v>
       </c>
@@ -7052,7 +7427,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <v>121328</v>
       </c>
@@ -7066,7 +7441,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
         <v>121329</v>
       </c>
@@ -7080,7 +7455,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <v>121330</v>
       </c>
@@ -7094,7 +7469,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
         <v>121332</v>
       </c>
@@ -7108,7 +7483,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <v>121333</v>
       </c>
@@ -7122,7 +7497,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
         <v>121401</v>
       </c>
@@ -7136,7 +7511,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <v>121402</v>
       </c>
@@ -7150,7 +7525,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
         <v>121403</v>
       </c>
@@ -7164,7 +7539,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <v>121404</v>
       </c>
@@ -7178,7 +7553,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
         <v>121405</v>
       </c>
@@ -7192,7 +7567,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <v>131501</v>
       </c>
@@ -7206,7 +7581,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
         <v>131502</v>
       </c>
@@ -7220,7 +7595,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <v>131503</v>
       </c>
@@ -7234,7 +7609,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
         <v>131504</v>
       </c>
@@ -7248,7 +7623,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <v>131505</v>
       </c>
@@ -7262,7 +7637,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
         <v>131506</v>
       </c>
@@ -7276,7 +7651,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
         <v>131507</v>
       </c>
@@ -7290,7 +7665,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
         <v>131508</v>
       </c>
@@ -7304,7 +7679,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
         <v>131509</v>
       </c>
@@ -7318,7 +7693,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
         <v>131511</v>
       </c>
@@ -7332,7 +7707,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
         <v>131515</v>
       </c>
@@ -7346,7 +7721,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
         <v>131519</v>
       </c>
@@ -7360,7 +7735,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
         <v>131524</v>
       </c>
@@ -7374,7 +7749,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
         <v>131525</v>
       </c>
@@ -7388,7 +7763,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
         <v>131526</v>
       </c>
@@ -7402,7 +7777,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
         <v>131527</v>
       </c>
@@ -7416,7 +7791,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <v>131528</v>
       </c>
@@ -7430,7 +7805,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <v>131529</v>
       </c>
@@ -7444,7 +7819,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <v>131531</v>
       </c>
@@ -7458,7 +7833,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
         <v>131534</v>
       </c>
@@ -7472,7 +7847,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
         <v>131536</v>
       </c>
@@ -7486,7 +7861,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="8">
         <v>131601</v>
       </c>
@@ -7500,7 +7875,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>131602</v>
       </c>
@@ -7514,7 +7889,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>141801</v>
       </c>
@@ -7528,7 +7903,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="8">
         <v>141802</v>
       </c>
@@ -7542,7 +7917,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="8">
         <v>141803</v>
       </c>
@@ -7556,7 +7931,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="8">
         <v>141804</v>
       </c>
@@ -7570,7 +7945,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="8">
         <v>141806</v>
       </c>
@@ -7584,7 +7959,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="8">
         <v>141807</v>
       </c>
@@ -7598,7 +7973,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="8">
         <v>141808</v>
       </c>
@@ -7612,7 +7987,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="8">
         <v>141809</v>
       </c>
@@ -7626,7 +8001,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="8">
         <v>141810</v>
       </c>
@@ -7640,7 +8015,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="8">
         <v>141811</v>
       </c>
@@ -7654,7 +8029,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="8">
         <v>141812</v>
       </c>
@@ -7668,7 +8043,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="8">
         <v>141901</v>
       </c>
@@ -7682,7 +8057,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="8">
         <v>141902</v>
       </c>
@@ -7696,7 +8071,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="8">
         <v>141903</v>
       </c>
@@ -7710,7 +8085,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="8">
         <v>141904</v>
       </c>
@@ -7724,7 +8099,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="8">
         <v>141905</v>
       </c>
@@ -7738,7 +8113,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="8">
         <v>141906</v>
       </c>
@@ -7752,7 +8127,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="8">
         <v>141907</v>
       </c>
@@ -7766,7 +8141,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="8">
         <v>141908</v>
       </c>
@@ -7780,7 +8155,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="8">
         <v>142001</v>
       </c>
@@ -7794,7 +8169,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="8">
         <v>142002</v>
       </c>
@@ -7808,7 +8183,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="8">
         <v>142101</v>
       </c>
@@ -7822,7 +8197,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="8">
         <v>142102</v>
       </c>
@@ -7836,7 +8211,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="8">
         <v>142103</v>
       </c>
@@ -7850,7 +8225,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="8">
         <v>142104</v>
       </c>
@@ -7864,7 +8239,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="8">
         <v>142105</v>
       </c>
@@ -7878,7 +8253,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="8">
         <v>142106</v>
       </c>
@@ -7892,7 +8267,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="8">
         <v>142107</v>
       </c>
@@ -7906,7 +8281,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
         <v>142108</v>
       </c>
@@ -7920,7 +8295,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="8">
         <v>142109</v>
       </c>
@@ -7934,7 +8309,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="8">
         <v>142201</v>
       </c>
@@ -7948,7 +8323,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="8">
         <v>142203</v>
       </c>
@@ -7962,7 +8337,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="5">
         <v>152301</v>
       </c>
@@ -7976,7 +8351,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="8">
         <v>152302</v>
       </c>
@@ -7990,7 +8365,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="8">
         <v>152304</v>
       </c>
@@ -8007,7 +8382,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="8">
         <v>152305</v>
       </c>
@@ -8021,7 +8396,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="8">
         <v>152306</v>
       </c>
@@ -8035,7 +8410,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="12">
         <v>152307</v>
       </c>
@@ -8052,7 +8427,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="8">
         <v>152309</v>
       </c>
@@ -8066,7 +8441,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="8">
         <v>152310</v>
       </c>
@@ -8080,7 +8455,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="8">
         <v>152312</v>
       </c>
@@ -8094,7 +8469,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="8">
         <v>152315</v>
       </c>
@@ -8108,7 +8483,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="8">
         <v>152316</v>
       </c>
@@ -8122,7 +8497,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="8">
         <v>152318</v>
       </c>
@@ -8136,7 +8511,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="8">
         <v>152322</v>
       </c>
@@ -8150,7 +8525,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="8">
         <v>152401</v>
       </c>
@@ -8164,7 +8539,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="8">
         <v>152404</v>
       </c>
@@ -8178,7 +8553,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="8">
         <v>152501</v>
       </c>
@@ -8192,7 +8567,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="8">
         <v>152506</v>
       </c>
@@ -8206,7 +8581,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="8">
         <v>152511</v>
       </c>
@@ -8220,7 +8595,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="8">
         <v>152512</v>
       </c>
@@ -8234,7 +8609,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="18">
         <v>152601</v>
       </c>
@@ -8248,7 +8623,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="5">
         <v>162701</v>
       </c>
@@ -8262,7 +8637,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="8">
         <v>162702</v>
       </c>
@@ -8276,7 +8651,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="8">
         <v>162703</v>
       </c>
@@ -8290,7 +8665,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="8">
         <v>162704</v>
       </c>
@@ -8304,7 +8679,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="8">
         <v>162705</v>
       </c>
@@ -8318,7 +8693,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="8">
         <v>162706</v>
       </c>
@@ -8332,7 +8707,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="8">
         <v>162707</v>
       </c>
@@ -8346,7 +8721,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="8">
         <v>162708</v>
       </c>
@@ -8360,7 +8735,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="8">
         <v>162709</v>
       </c>
@@ -8374,7 +8749,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="8">
         <v>162710</v>
       </c>
@@ -8388,7 +8763,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="8">
         <v>162711</v>
       </c>
@@ -8402,7 +8777,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="8">
         <v>162713</v>
       </c>
@@ -8419,7 +8794,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="12">
         <v>162716</v>
       </c>
@@ -8436,7 +8811,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="8">
         <v>162801</v>
       </c>
@@ -8450,7 +8825,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="8">
         <v>162802</v>
       </c>
@@ -8464,7 +8839,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="8">
         <v>162804</v>
       </c>
@@ -8478,7 +8853,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="8">
         <v>162805</v>
       </c>
@@ -8492,7 +8867,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="8">
         <v>162806</v>
       </c>
@@ -8509,7 +8884,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="12">
         <v>162807</v>
       </c>
@@ -8526,7 +8901,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="12">
         <v>162808</v>
       </c>
@@ -8543,7 +8918,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="8">
         <v>162901</v>
       </c>
@@ -8557,7 +8932,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="8">
         <v>163001</v>
       </c>
@@ -8571,7 +8946,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="8">
         <v>163101</v>
       </c>
@@ -8585,7 +8960,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="8">
         <v>163102</v>
       </c>
@@ -8599,7 +8974,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="8">
         <v>163103</v>
       </c>
@@ -8613,7 +8988,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="8">
         <v>163104</v>
       </c>
@@ -8627,7 +9002,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="8">
         <v>163105</v>
       </c>
@@ -8641,7 +9016,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="8">
         <v>163106</v>
       </c>
@@ -8655,7 +9030,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="8">
         <v>163107</v>
       </c>
@@ -8669,7 +9044,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="8">
         <v>163108</v>
       </c>
@@ -8683,7 +9058,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="8">
         <v>163201</v>
       </c>
@@ -8697,7 +9072,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="8">
         <v>163203</v>
       </c>
@@ -8711,7 +9086,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="8">
         <v>163206</v>
       </c>
@@ -8725,7 +9100,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="8">
         <v>163301</v>
       </c>
@@ -8739,7 +9114,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="8">
         <v>163303</v>
       </c>
@@ -8753,7 +9128,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="8">
         <v>163304</v>
       </c>
@@ -8767,7 +9142,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="18">
         <v>163406</v>
       </c>
@@ -8781,7 +9156,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="261" spans="1:4" s="24" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:4" s="24" customFormat="1" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="21">
         <v>170202</v>
       </c>
@@ -8795,7 +9170,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="262" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="25">
         <v>170203</v>
       </c>
@@ -8809,7 +9184,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="263" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="28">
         <v>170204</v>
       </c>
@@ -8823,7 +9198,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="264" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="28">
         <v>170205</v>
       </c>
@@ -8837,7 +9212,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="265" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="28">
         <v>170206</v>
       </c>
@@ -8851,7 +9226,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="266" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="28">
         <v>170207</v>
       </c>
@@ -8865,7 +9240,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="267" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="28">
         <v>170208</v>
       </c>
@@ -8879,7 +9254,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="268" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="28">
         <v>170209</v>
       </c>
@@ -8893,7 +9268,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="269" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="28">
         <v>170210</v>
       </c>
@@ -8907,7 +9282,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="270" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="28">
         <v>170211</v>
       </c>
@@ -8921,7 +9296,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="271" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="28">
         <v>170212</v>
       </c>
@@ -8935,7 +9310,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="272" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="28">
         <v>170213</v>
       </c>
@@ -8949,7 +9324,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="273" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="28">
         <v>170214</v>
       </c>
@@ -8963,7 +9338,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="274" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="28">
         <v>170215</v>
       </c>
@@ -8977,7 +9352,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="275" spans="1:5" s="24" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:5" s="24" customFormat="1" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="31">
         <v>170216</v>
       </c>
@@ -8994,7 +9369,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="34">
         <v>177777</v>
       </c>
@@ -9008,7 +9383,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="36">
         <v>180001</v>
       </c>
@@ -9022,7 +9397,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="5">
         <v>90001</v>
       </c>
@@ -9036,7 +9411,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="8">
         <v>90002</v>
       </c>
@@ -9050,7 +9425,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="8">
         <v>90003</v>
       </c>
@@ -9064,7 +9439,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="8">
         <v>90004</v>
       </c>
@@ -9078,7 +9453,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="8">
         <v>90005</v>
       </c>
@@ -9092,7 +9467,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="8">
         <v>90006</v>
       </c>
@@ -9106,7 +9481,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="8">
         <v>90007</v>
       </c>
@@ -9120,7 +9495,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="8">
         <v>90008</v>
       </c>
@@ -9134,7 +9509,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="8">
         <v>90009</v>
       </c>
@@ -9148,7 +9523,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="8">
         <v>90010</v>
       </c>
@@ -9162,7 +9537,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="8">
         <v>90011</v>
       </c>
@@ -9176,7 +9551,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="8">
         <v>90012</v>
       </c>
@@ -9190,7 +9565,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="8">
         <v>90013</v>
       </c>
@@ -9204,7 +9579,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="8">
         <v>90014</v>
       </c>
@@ -9218,7 +9593,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="8">
         <v>90015</v>
       </c>
@@ -9232,7 +9607,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="8">
         <v>90016</v>
       </c>
@@ -9246,7 +9621,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="8">
         <v>90017</v>
       </c>
@@ -9260,7 +9635,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="8">
         <v>90018</v>
       </c>
@@ -9274,7 +9649,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="8">
         <v>90019</v>
       </c>
@@ -9288,7 +9663,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="8">
         <v>90020</v>
       </c>
@@ -9302,7 +9677,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="8">
         <v>90021</v>
       </c>
@@ -9316,7 +9691,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="8">
         <v>90022</v>
       </c>
@@ -9330,7 +9705,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="8">
         <v>90023</v>
       </c>
@@ -9344,7 +9719,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="8">
         <v>90024</v>
       </c>
@@ -9358,7 +9733,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="8">
         <v>90025</v>
       </c>
@@ -9372,7 +9747,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="8">
         <v>90026</v>
       </c>
@@ -9386,7 +9761,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="8">
         <v>90027</v>
       </c>
@@ -9400,7 +9775,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="8">
         <v>90028</v>
       </c>
@@ -9414,7 +9789,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="8">
         <v>90029</v>
       </c>
@@ -9428,7 +9803,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="8">
         <v>90030</v>
       </c>
@@ -9442,7 +9817,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="8">
         <v>90031</v>
       </c>
@@ -9456,7 +9831,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="8">
         <v>90032</v>
       </c>
@@ -9470,7 +9845,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="8">
         <v>90033</v>
       </c>
@@ -9484,7 +9859,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="8">
         <v>90034</v>
       </c>
@@ -9498,7 +9873,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="8">
         <v>90035</v>
       </c>
@@ -9512,7 +9887,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="8">
         <v>90036</v>
       </c>
@@ -9526,7 +9901,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="8">
         <v>90037</v>
       </c>
@@ -9540,7 +9915,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="8">
         <v>90038</v>
       </c>
@@ -9554,7 +9929,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="8">
         <v>90039</v>
       </c>
@@ -9568,7 +9943,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="8">
         <v>90040</v>
       </c>
@@ -9582,7 +9957,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="72">
         <v>999999</v>
       </c>
@@ -9606,24 +9981,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3F87FA4-8AE3-4E4F-AF33-D2B7AA208BA0}">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E204"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="41" customWidth="1"/>
+    <col min="1" max="1" width="11.2109375" style="41" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="42" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="68" customWidth="1"/>
-    <col min="5" max="5" width="34.125" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" style="41" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
@@ -9632,7 +10007,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="89" t="s">
         <v>1</v>
       </c>
@@ -9646,7 +10021,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="46">
         <v>210101</v>
       </c>
@@ -9660,7 +10035,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="48">
         <v>210102</v>
       </c>
@@ -9674,7 +10049,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="48">
         <v>210103</v>
       </c>
@@ -9688,7 +10063,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="48">
         <v>210104</v>
       </c>
@@ -9702,7 +10077,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="48">
         <v>210105</v>
       </c>
@@ -9716,7 +10091,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="48">
         <v>210106</v>
       </c>
@@ -9730,7 +10105,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="48">
         <v>210107</v>
       </c>
@@ -9744,7 +10119,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="48">
         <v>210108</v>
       </c>
@@ -9758,7 +10133,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="48">
         <v>210109</v>
       </c>
@@ -9772,7 +10147,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="48">
         <v>210110</v>
       </c>
@@ -9786,7 +10161,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="48">
         <v>210112</v>
       </c>
@@ -9800,7 +10175,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="48">
         <v>210113</v>
       </c>
@@ -9814,7 +10189,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="48">
         <v>210114</v>
       </c>
@@ -9828,7 +10203,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="48">
         <v>210115</v>
       </c>
@@ -9842,7 +10217,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="48">
         <v>210116</v>
       </c>
@@ -9856,7 +10231,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="48">
         <v>210117</v>
       </c>
@@ -9870,7 +10245,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="48">
         <v>210118</v>
       </c>
@@ -9884,7 +10259,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="48">
         <v>210119</v>
       </c>
@@ -9898,7 +10273,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="48">
         <v>210120</v>
       </c>
@@ -9915,7 +10290,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="50">
         <v>210121</v>
       </c>
@@ -9932,7 +10307,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="48">
         <v>210123</v>
       </c>
@@ -9946,7 +10321,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="52">
         <v>210124</v>
       </c>
@@ -9960,7 +10335,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="48">
         <v>210125</v>
       </c>
@@ -9974,7 +10349,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="48">
         <v>210201</v>
       </c>
@@ -9988,7 +10363,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="48">
         <v>210202</v>
       </c>
@@ -10002,7 +10377,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="48">
         <v>210204</v>
       </c>
@@ -10016,7 +10391,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="48">
         <v>210301</v>
       </c>
@@ -10030,7 +10405,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="48">
         <v>210401</v>
       </c>
@@ -10044,7 +10419,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="48">
         <v>210402</v>
       </c>
@@ -10058,7 +10433,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="48">
         <v>210403</v>
       </c>
@@ -10072,7 +10447,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="48">
         <v>210501</v>
       </c>
@@ -10086,7 +10461,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="48">
         <v>210502</v>
       </c>
@@ -10100,7 +10475,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="48">
         <v>210503</v>
       </c>
@@ -10114,7 +10489,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="48">
         <v>210504</v>
       </c>
@@ -10128,7 +10503,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="48">
         <v>210505</v>
       </c>
@@ -10142,7 +10517,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="48">
         <v>210506</v>
       </c>
@@ -10156,7 +10531,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="48">
         <v>210601</v>
       </c>
@@ -10170,7 +10545,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="48">
         <v>210602</v>
       </c>
@@ -10184,7 +10559,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="48">
         <v>210603</v>
       </c>
@@ -10198,7 +10573,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="48">
         <v>210701</v>
       </c>
@@ -10212,7 +10587,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="48">
         <v>210702</v>
       </c>
@@ -10226,7 +10601,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="52">
         <v>210801</v>
       </c>
@@ -10240,7 +10615,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="48">
         <v>210802</v>
       </c>
@@ -10254,7 +10629,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="48">
         <v>210803</v>
       </c>
@@ -10268,7 +10643,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="54">
         <v>210804</v>
       </c>
@@ -10282,7 +10657,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="52">
         <v>220901</v>
       </c>
@@ -10296,7 +10671,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="48">
         <v>220902</v>
       </c>
@@ -10310,7 +10685,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="48">
         <v>220903</v>
       </c>
@@ -10324,7 +10699,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="48">
         <v>220904</v>
       </c>
@@ -10338,7 +10713,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="48">
         <v>220905</v>
       </c>
@@ -10352,7 +10727,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="48">
         <v>220906</v>
       </c>
@@ -10366,7 +10741,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="48">
         <v>220907</v>
       </c>
@@ -10380,7 +10755,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="48">
         <v>220908</v>
       </c>
@@ -10394,7 +10769,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="48">
         <v>220909</v>
       </c>
@@ -10408,7 +10783,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="48">
         <v>220910</v>
       </c>
@@ -10422,7 +10797,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="48">
         <v>220911</v>
       </c>
@@ -10436,7 +10811,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="48">
         <v>221001</v>
       </c>
@@ -10450,7 +10825,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="48">
         <v>221002</v>
       </c>
@@ -10464,7 +10839,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="48">
         <v>221003</v>
       </c>
@@ -10478,7 +10853,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="48">
         <v>221101</v>
       </c>
@@ -10492,7 +10867,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="48">
         <v>221102</v>
       </c>
@@ -10509,7 +10884,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="50">
         <v>221103</v>
       </c>
@@ -10526,7 +10901,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="48">
         <v>221104</v>
       </c>
@@ -10540,7 +10915,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="48">
         <v>221105</v>
       </c>
@@ -10554,7 +10929,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="48">
         <v>221106</v>
       </c>
@@ -10568,7 +10943,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="48">
         <v>221107</v>
       </c>
@@ -10582,7 +10957,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="48">
         <v>221108</v>
       </c>
@@ -10596,7 +10971,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="48">
         <v>221109</v>
       </c>
@@ -10610,7 +10985,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="52">
         <v>221201</v>
       </c>
@@ -10624,7 +10999,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="54">
         <v>221202</v>
       </c>
@@ -10638,7 +11013,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="52">
         <v>231301</v>
       </c>
@@ -10652,7 +11027,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="48">
         <v>231302</v>
       </c>
@@ -10666,7 +11041,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="48">
         <v>231303</v>
       </c>
@@ -10680,7 +11055,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="48">
         <v>231304</v>
       </c>
@@ -10694,7 +11069,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="48">
         <v>231307</v>
       </c>
@@ -10708,7 +11083,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="48">
         <v>231308</v>
       </c>
@@ -10722,7 +11097,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="48">
         <v>231309</v>
       </c>
@@ -10736,7 +11111,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="48">
         <v>231401</v>
       </c>
@@ -10750,7 +11125,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="48">
         <v>231501</v>
       </c>
@@ -10764,7 +11139,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="48">
         <v>231502</v>
       </c>
@@ -10778,7 +11153,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="48">
         <v>231504</v>
       </c>
@@ -10792,7 +11167,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="48">
         <v>231505</v>
       </c>
@@ -10806,7 +11181,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="48">
         <v>231506</v>
       </c>
@@ -10820,7 +11195,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="48">
         <v>231507</v>
       </c>
@@ -10834,7 +11209,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="48">
         <v>231509</v>
       </c>
@@ -10848,7 +11223,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="48">
         <v>231510</v>
       </c>
@@ -10862,7 +11237,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="48">
         <v>231511</v>
       </c>
@@ -10876,7 +11251,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="48">
         <v>231513</v>
       </c>
@@ -10890,7 +11265,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="48">
         <v>231516</v>
       </c>
@@ -10904,7 +11279,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="48">
         <v>231517</v>
       </c>
@@ -10918,7 +11293,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="48">
         <v>231518</v>
       </c>
@@ -10932,7 +11307,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="48">
         <v>231519</v>
       </c>
@@ -10946,7 +11321,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="54">
         <v>231601</v>
       </c>
@@ -10960,7 +11335,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="52">
         <v>241801</v>
       </c>
@@ -10974,7 +11349,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="48">
         <v>241802</v>
       </c>
@@ -10988,7 +11363,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="48">
         <v>241804</v>
       </c>
@@ -11002,7 +11377,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="48">
         <v>241901</v>
       </c>
@@ -11016,7 +11391,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="48">
         <v>241903</v>
       </c>
@@ -11030,7 +11405,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="48">
         <v>242001</v>
       </c>
@@ -11044,7 +11419,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="48">
         <v>242101</v>
       </c>
@@ -11058,7 +11433,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="48">
         <v>242102</v>
       </c>
@@ -11072,7 +11447,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="48">
         <v>242103</v>
       </c>
@@ -11086,7 +11461,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="48">
         <v>242104</v>
       </c>
@@ -11100,7 +11475,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="48">
         <v>242105</v>
       </c>
@@ -11114,7 +11489,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="48">
         <v>242201</v>
       </c>
@@ -11128,7 +11503,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="54">
         <v>242202</v>
       </c>
@@ -11142,7 +11517,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="52">
         <v>252301</v>
       </c>
@@ -11156,7 +11531,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="48">
         <v>252302</v>
       </c>
@@ -11170,7 +11545,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="48">
         <v>252303</v>
       </c>
@@ -11184,7 +11559,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="48">
         <v>252304</v>
       </c>
@@ -11198,7 +11573,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="48">
         <v>252305</v>
       </c>
@@ -11212,7 +11587,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="48">
         <v>252306</v>
       </c>
@@ -11226,7 +11601,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="48">
         <v>252307</v>
       </c>
@@ -11240,7 +11615,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="48">
         <v>252308</v>
       </c>
@@ -11254,7 +11629,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="48">
         <v>252309</v>
       </c>
@@ -11268,7 +11643,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="48">
         <v>252310</v>
       </c>
@@ -11282,7 +11657,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="48">
         <v>252311</v>
       </c>
@@ -11296,7 +11671,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="48">
         <v>252402</v>
       </c>
@@ -11310,7 +11685,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="48">
         <v>252501</v>
       </c>
@@ -11324,7 +11699,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="48">
         <v>252503</v>
       </c>
@@ -11338,7 +11713,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="48">
         <v>252505</v>
       </c>
@@ -11352,7 +11727,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="56">
         <v>252601</v>
       </c>
@@ -11366,7 +11741,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="52">
         <v>262701</v>
       </c>
@@ -11383,7 +11758,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="48">
         <v>262702</v>
       </c>
@@ -11400,7 +11775,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="50">
         <v>262703</v>
       </c>
@@ -11417,7 +11792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="50">
         <v>262704</v>
       </c>
@@ -11434,7 +11809,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="50">
         <v>262705</v>
       </c>
@@ -11451,7 +11826,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="48">
         <v>262706</v>
       </c>
@@ -11465,7 +11840,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="50">
         <v>262707</v>
       </c>
@@ -11482,7 +11857,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="48">
         <v>262709</v>
       </c>
@@ -11496,7 +11871,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="48">
         <v>262801</v>
       </c>
@@ -11510,7 +11885,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="48">
         <v>262901</v>
       </c>
@@ -11524,7 +11899,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="48">
         <v>263001</v>
       </c>
@@ -11538,7 +11913,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="48">
         <v>263003</v>
       </c>
@@ -11552,7 +11927,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="48">
         <v>263004</v>
       </c>
@@ -11566,7 +11941,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="48">
         <v>263101</v>
       </c>
@@ -11580,7 +11955,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="48">
         <v>263103</v>
       </c>
@@ -11594,7 +11969,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="48">
         <v>263104</v>
       </c>
@@ -11608,7 +11983,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="48">
         <v>263201</v>
       </c>
@@ -11622,7 +11997,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="48">
         <v>263301</v>
       </c>
@@ -11636,7 +12011,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="48">
         <v>263401</v>
       </c>
@@ -11650,7 +12025,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="58">
         <v>263404</v>
       </c>
@@ -11664,7 +12039,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="44">
         <v>270001</v>
       </c>
@@ -11678,7 +12053,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="44">
         <v>270202</v>
       </c>
@@ -11692,7 +12067,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="46">
         <v>270203</v>
       </c>
@@ -11706,7 +12081,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="48">
         <v>270204</v>
       </c>
@@ -11720,7 +12095,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="48">
         <v>270205</v>
       </c>
@@ -11734,7 +12109,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="48">
         <v>270206</v>
       </c>
@@ -11748,7 +12123,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="48">
         <v>270207</v>
       </c>
@@ -11762,7 +12137,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="48">
         <v>270208</v>
       </c>
@@ -11776,7 +12151,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="48">
         <v>270209</v>
       </c>
@@ -11790,7 +12165,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="48">
         <v>270210</v>
       </c>
@@ -11804,7 +12179,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="48">
         <v>270211</v>
       </c>
@@ -11818,7 +12193,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="48">
         <v>270212</v>
       </c>
@@ -11832,7 +12207,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="48">
         <v>270213</v>
       </c>
@@ -11846,7 +12221,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="48">
         <v>270214</v>
       </c>
@@ -11860,7 +12235,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="48">
         <v>270215</v>
       </c>
@@ -11874,7 +12249,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="60">
         <v>270216</v>
       </c>
@@ -11891,7 +12266,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="61">
         <v>280001</v>
       </c>
@@ -11905,7 +12280,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="162" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="63">
         <v>90001</v>
       </c>
@@ -11919,7 +12294,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="163" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="66">
         <v>90002</v>
       </c>
@@ -11933,7 +12308,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="164" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="66">
         <v>90003</v>
       </c>
@@ -11947,7 +12322,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="165" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="66">
         <v>90004</v>
       </c>
@@ -11961,7 +12336,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="166" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="66">
         <v>90005</v>
       </c>
@@ -11975,7 +12350,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="167" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="66">
         <v>90006</v>
       </c>
@@ -11989,7 +12364,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="168" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="66">
         <v>90007</v>
       </c>
@@ -12003,7 +12378,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="169" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="66">
         <v>90008</v>
       </c>
@@ -12017,7 +12392,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="170" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="66">
         <v>90009</v>
       </c>
@@ -12031,7 +12406,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="171" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="66">
         <v>90010</v>
       </c>
@@ -12045,7 +12420,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="172" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="66">
         <v>90011</v>
       </c>
@@ -12059,7 +12434,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="173" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="66">
         <v>90012</v>
       </c>
@@ -12073,7 +12448,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="174" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="66">
         <v>90013</v>
       </c>
@@ -12087,7 +12462,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="175" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="66">
         <v>90014</v>
       </c>
@@ -12101,7 +12476,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="176" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="66">
         <v>90015</v>
       </c>
@@ -12115,7 +12490,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="177" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="66">
         <v>90016</v>
       </c>
@@ -12129,7 +12504,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="178" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="66">
         <v>90017</v>
       </c>
@@ -12143,7 +12518,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="179" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="66">
         <v>90018</v>
       </c>
@@ -12157,7 +12532,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="180" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="66">
         <v>90019</v>
       </c>
@@ -12171,7 +12546,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="181" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="66">
         <v>90020</v>
       </c>
@@ -12185,7 +12560,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="182" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="66">
         <v>90021</v>
       </c>
@@ -12199,7 +12574,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="183" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="66">
         <v>90022</v>
       </c>
@@ -12213,7 +12588,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="66">
         <v>90023</v>
       </c>
@@ -12227,7 +12602,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="185" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="66">
         <v>90024</v>
       </c>
@@ -12241,7 +12616,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="186" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="66">
         <v>90025</v>
       </c>
@@ -12255,7 +12630,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="187" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="66">
         <v>90026</v>
       </c>
@@ -12269,7 +12644,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="188" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="66">
         <v>90027</v>
       </c>
@@ -12283,7 +12658,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="189" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="66">
         <v>90028</v>
       </c>
@@ -12297,7 +12672,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="190" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="66">
         <v>90029</v>
       </c>
@@ -12311,7 +12686,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="191" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="66">
         <v>90030</v>
       </c>
@@ -12325,7 +12700,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="192" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="66">
         <v>90031</v>
       </c>
@@ -12339,7 +12714,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="193" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="66">
         <v>90032</v>
       </c>
@@ -12353,7 +12728,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="194" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="66">
         <v>90033</v>
       </c>
@@ -12367,7 +12742,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="195" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="66">
         <v>90034</v>
       </c>
@@ -12381,7 +12756,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="196" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="66">
         <v>90035</v>
       </c>
@@ -12395,7 +12770,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="197" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="66">
         <v>90036</v>
       </c>
@@ -12409,7 +12784,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="198" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="66">
         <v>90037</v>
       </c>
@@ -12423,7 +12798,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="199" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="66">
         <v>90038</v>
       </c>
@@ -12437,7 +12812,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="200" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="66">
         <v>90039</v>
       </c>
@@ -12451,7 +12826,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="201" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="66">
         <v>90040</v>
       </c>
@@ -12465,7 +12840,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="58">
         <v>999999</v>
       </c>
@@ -12479,7 +12854,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="42"/>
     </row>
   </sheetData>

--- a/R8_県学調_問題マスタ.xlsx
+++ b/R8_県学調_問題マスタ.xlsx
@@ -5,25 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9149d06814ece6b4/github/survey-dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{14723A84-59D9-41EF-B850-FD79EA8212AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93FE0F33-093A-4B05-BCA0-A5E5017E3E65}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52852236-5613-49CD-BF73-FA596432BFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="問題マスタ" sheetId="6" r:id="rId1"/>
     <sheet name="選択肢マスタ" sheetId="7" r:id="rId2"/>
-    <sheet name="小学校コード一覧表" sheetId="2" state="hidden" r:id="rId3"/>
-    <sheet name="中学校コード一覧表" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="県データ" sheetId="8" r:id="rId3"/>
+    <sheet name="小学校コード一覧表" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="中学校コード一覧表" sheetId="3" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">小学校コード一覧表!$A$2:$D$318</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">小学校コード一覧表!$A$1:$E$318</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">中学校コード一覧表!$A$1:$E$202</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">小学校コード一覧表!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">中学校コード一覧表!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">小学校コード一覧表!$A$2:$D$318</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">小学校コード一覧表!$A$1:$E$318</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">中学校コード一覧表!$A$1:$E$202</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">小学校コード一覧表!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">中学校コード一覧表!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="745">
   <si>
     <t>学校コード一覧表</t>
     <rPh sb="0" eb="2">
@@ -2989,6 +2990,100 @@
   </si>
   <si>
     <t>Q5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ種別</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>対象コード</t>
+  </si>
+  <si>
+    <t>対象名</t>
+  </si>
+  <si>
+    <t>領域</t>
+  </si>
+  <si>
+    <t>得点帯下限</t>
+  </si>
+  <si>
+    <t>得点帯上限</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>人数</t>
+  </si>
+  <si>
+    <t>母数</t>
+  </si>
+  <si>
+    <t>summary</t>
+  </si>
+  <si>
+    <t>参加人数</t>
+  </si>
+  <si>
+    <t>pref</t>
+  </si>
+  <si>
+    <t>県全体</t>
+  </si>
+  <si>
+    <t>平均点</t>
+  </si>
+  <si>
+    <t>最高点</t>
+  </si>
+  <si>
+    <t>最低点</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>中央値</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>満点</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>正答率</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>Q7</t>
+  </si>
+  <si>
+    <t>score_dist</t>
+  </si>
+  <si>
+    <t>度数</t>
+  </si>
+  <si>
+    <t>\frac{7}{4}</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4070,10 +4165,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92E6BF46-C548-4809-AABD-EC782FD1660F}" name="テーブル4" displayName="テーブル4" ref="A1:S27" totalsRowShown="0">
   <autoFilter ref="A1:S27" xr:uid="{92E6BF46-C548-4809-AABD-EC782FD1660F}"/>
@@ -4121,6 +4212,27 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7861881-F35C-4F9F-83E7-28DEA30120B9}" name="テーブル5" displayName="テーブル5" ref="A1:L24" totalsRowShown="0">
+  <autoFilter ref="A1:L24" xr:uid="{E7861881-F35C-4F9F-83E7-28DEA30120B9}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{4FBC1E99-EAAC-4C62-8637-41F045BE22DF}" name="データ種別"/>
+    <tableColumn id="2" xr3:uid="{F474E028-1DCA-4D5D-A7D9-1EA8C1A73AAC}" name="項目"/>
+    <tableColumn id="3" xr3:uid="{C74D751A-10AA-499D-9ED4-736185620955}" name="対象コード"/>
+    <tableColumn id="4" xr3:uid="{18900A38-0CA9-4E88-909D-68A65A0407B6}" name="対象名"/>
+    <tableColumn id="5" xr3:uid="{970D1D75-5606-4BAF-8009-4362ECE98FC6}" name="問題番号"/>
+    <tableColumn id="6" xr3:uid="{A140F5EB-71A1-4686-9C5C-0A3ACC2BB230}" name="領域"/>
+    <tableColumn id="7" xr3:uid="{ED620320-570A-4B51-99E7-8112BD72B86F}" name="得点帯下限"/>
+    <tableColumn id="8" xr3:uid="{DF966F7D-C7CE-4315-AF32-E42AF9B690A2}" name="得点帯上限"/>
+    <tableColumn id="9" xr3:uid="{7B71ECBE-9330-406C-A3FC-D42A8D20679E}" name="値"/>
+    <tableColumn id="10" xr3:uid="{4B5AC634-A338-4767-94CE-5AFA9CFC393A}" name="人数"/>
+    <tableColumn id="11" xr3:uid="{0445B3DC-E780-43B6-A9EA-A5BDAE8A8E56}" name="母数"/>
+    <tableColumn id="12" xr3:uid="{23597A53-8D86-4D84-BD7B-55A26D583360}" name="備考"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BAA040B5-8ED9-4622-B97A-11270A60D126}" name="_tablesho" displayName="_tablesho" ref="A2:D318" totalsRowShown="0" tableBorderDxfId="9">
   <autoFilter ref="A2:D318" xr:uid="{BAA040B5-8ED9-4622-B97A-11270A60D126}"/>
   <tableColumns count="4">
@@ -4133,7 +4245,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9B11CD57-71E2-4773-9D23-F8794F6BC098}" name="_tablechu" displayName="_tablechu" ref="A2:D202" totalsRowShown="0" tableBorderDxfId="4">
   <autoFilter ref="A2:D202" xr:uid="{9B11CD57-71E2-4773-9D23-F8794F6BC098}"/>
   <tableColumns count="4">
@@ -4410,20 +4522,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731ACD8B-3F3F-4FB8-AC79-3009D1AB82F2}">
   <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="3" width="10.2109375" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.2109375" customWidth="1"/>
+    <col min="2" max="3" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.25" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.85546875" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" customWidth="1"/>
-    <col min="13" max="13" width="10.2109375" customWidth="1"/>
-    <col min="16" max="16" width="10.2109375" customWidth="1"/>
+    <col min="10" max="11" width="16.875" customWidth="1"/>
+    <col min="12" max="12" width="19.875" customWidth="1"/>
+    <col min="13" max="13" width="10.25" customWidth="1"/>
+    <col min="16" max="16" width="10.25" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>655</v>
       </c>
@@ -4482,7 +4594,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>566</v>
       </c>
@@ -4538,7 +4650,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>580</v>
       </c>
@@ -4594,7 +4706,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>588</v>
       </c>
@@ -4650,7 +4762,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>596</v>
       </c>
@@ -4706,7 +4818,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>601</v>
       </c>
@@ -4762,7 +4874,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>608</v>
       </c>
@@ -4815,7 +4927,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>613</v>
       </c>
@@ -4861,6 +4973,9 @@
       <c r="O8" t="s">
         <v>576</v>
       </c>
+      <c r="P8" t="s">
+        <v>744</v>
+      </c>
       <c r="Q8" t="s">
         <v>577</v>
       </c>
@@ -4868,7 +4983,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>619</v>
       </c>
@@ -4924,7 +5039,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>625</v>
       </c>
@@ -4980,7 +5095,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>630</v>
       </c>
@@ -5033,7 +5148,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>636</v>
       </c>
@@ -5089,7 +5204,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>646</v>
       </c>
@@ -5145,7 +5260,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>650</v>
       </c>
@@ -5201,7 +5316,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>654</v>
       </c>
@@ -5218,16 +5333,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33C08DAF-9E90-4F71-B777-114760BC3106}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.92578125" customWidth="1"/>
+    <col min="1" max="1" width="9.875" customWidth="1"/>
     <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.640625" customWidth="1"/>
+    <col min="3" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="9" max="9" width="51.92578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="51.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>681</v>
       </c>
@@ -5256,7 +5371,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>712</v>
       </c>
@@ -5285,7 +5400,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>712</v>
       </c>
@@ -5314,7 +5429,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>712</v>
       </c>
@@ -5343,7 +5458,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>712</v>
       </c>
@@ -5372,7 +5487,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>713</v>
       </c>
@@ -5401,7 +5516,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>713</v>
       </c>
@@ -5430,7 +5545,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>713</v>
       </c>
@@ -5470,23 +5585,609 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D793BDE-8574-4356-BF6F-65AC154CE378}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1" t="s">
+        <v>715</v>
+      </c>
+      <c r="C1" t="s">
+        <v>716</v>
+      </c>
+      <c r="D1" t="s">
+        <v>717</v>
+      </c>
+      <c r="E1" t="s">
+        <v>681</v>
+      </c>
+      <c r="F1" t="s">
+        <v>718</v>
+      </c>
+      <c r="G1" t="s">
+        <v>719</v>
+      </c>
+      <c r="H1" t="s">
+        <v>720</v>
+      </c>
+      <c r="I1" t="s">
+        <v>721</v>
+      </c>
+      <c r="J1" t="s">
+        <v>722</v>
+      </c>
+      <c r="K1" t="s">
+        <v>723</v>
+      </c>
+      <c r="L1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D2" t="s">
+        <v>727</v>
+      </c>
+      <c r="I2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>724</v>
+      </c>
+      <c r="B3" t="s">
+        <v>728</v>
+      </c>
+      <c r="C3" t="s">
+        <v>726</v>
+      </c>
+      <c r="D3" t="s">
+        <v>727</v>
+      </c>
+      <c r="I3">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>724</v>
+      </c>
+      <c r="B4" t="s">
+        <v>729</v>
+      </c>
+      <c r="C4" t="s">
+        <v>726</v>
+      </c>
+      <c r="D4" t="s">
+        <v>727</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>724</v>
+      </c>
+      <c r="B5" t="s">
+        <v>730</v>
+      </c>
+      <c r="C5" t="s">
+        <v>726</v>
+      </c>
+      <c r="D5" t="s">
+        <v>727</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>724</v>
+      </c>
+      <c r="B6" t="s">
+        <v>731</v>
+      </c>
+      <c r="C6" t="s">
+        <v>726</v>
+      </c>
+      <c r="D6" t="s">
+        <v>727</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>724</v>
+      </c>
+      <c r="B7" t="s">
+        <v>732</v>
+      </c>
+      <c r="C7" t="s">
+        <v>726</v>
+      </c>
+      <c r="D7" t="s">
+        <v>727</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>724</v>
+      </c>
+      <c r="B8" t="s">
+        <v>733</v>
+      </c>
+      <c r="C8" t="s">
+        <v>726</v>
+      </c>
+      <c r="D8" t="s">
+        <v>727</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>724</v>
+      </c>
+      <c r="B9" t="s">
+        <v>734</v>
+      </c>
+      <c r="C9" t="s">
+        <v>726</v>
+      </c>
+      <c r="D9" t="s">
+        <v>727</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>735</v>
+      </c>
+      <c r="B10" t="s">
+        <v>736</v>
+      </c>
+      <c r="C10" t="s">
+        <v>726</v>
+      </c>
+      <c r="D10" t="s">
+        <v>727</v>
+      </c>
+      <c r="E10" t="s">
+        <v>731</v>
+      </c>
+      <c r="F10" t="s">
+        <v>673</v>
+      </c>
+      <c r="I10">
+        <v>72.5</v>
+      </c>
+      <c r="K10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>735</v>
+      </c>
+      <c r="B11" t="s">
+        <v>736</v>
+      </c>
+      <c r="C11" t="s">
+        <v>726</v>
+      </c>
+      <c r="D11" t="s">
+        <v>727</v>
+      </c>
+      <c r="E11" t="s">
+        <v>737</v>
+      </c>
+      <c r="F11" t="s">
+        <v>673</v>
+      </c>
+      <c r="I11">
+        <v>68.099999999999994</v>
+      </c>
+      <c r="K11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>735</v>
+      </c>
+      <c r="B12" t="s">
+        <v>736</v>
+      </c>
+      <c r="C12" t="s">
+        <v>726</v>
+      </c>
+      <c r="D12" t="s">
+        <v>727</v>
+      </c>
+      <c r="E12" t="s">
+        <v>733</v>
+      </c>
+      <c r="F12" t="s">
+        <v>674</v>
+      </c>
+      <c r="I12">
+        <v>55.4</v>
+      </c>
+      <c r="K12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>735</v>
+      </c>
+      <c r="B13" t="s">
+        <v>736</v>
+      </c>
+      <c r="C13" t="s">
+        <v>726</v>
+      </c>
+      <c r="D13" t="s">
+        <v>727</v>
+      </c>
+      <c r="E13" t="s">
+        <v>738</v>
+      </c>
+      <c r="F13" t="s">
+        <v>675</v>
+      </c>
+      <c r="I13">
+        <v>61.8</v>
+      </c>
+      <c r="K13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>735</v>
+      </c>
+      <c r="B14" t="s">
+        <v>736</v>
+      </c>
+      <c r="C14" t="s">
+        <v>726</v>
+      </c>
+      <c r="D14" t="s">
+        <v>727</v>
+      </c>
+      <c r="E14" t="s">
+        <v>739</v>
+      </c>
+      <c r="F14" t="s">
+        <v>676</v>
+      </c>
+      <c r="I14">
+        <v>74.2</v>
+      </c>
+      <c r="K14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>735</v>
+      </c>
+      <c r="B15" t="s">
+        <v>736</v>
+      </c>
+      <c r="C15" t="s">
+        <v>726</v>
+      </c>
+      <c r="D15" t="s">
+        <v>727</v>
+      </c>
+      <c r="E15" t="s">
+        <v>740</v>
+      </c>
+      <c r="F15" t="s">
+        <v>677</v>
+      </c>
+      <c r="I15">
+        <v>49.7</v>
+      </c>
+      <c r="K15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>735</v>
+      </c>
+      <c r="B16" t="s">
+        <v>736</v>
+      </c>
+      <c r="C16" t="s">
+        <v>726</v>
+      </c>
+      <c r="D16" t="s">
+        <v>727</v>
+      </c>
+      <c r="E16" t="s">
+        <v>741</v>
+      </c>
+      <c r="F16" t="s">
+        <v>677</v>
+      </c>
+      <c r="I16">
+        <v>58.9</v>
+      </c>
+      <c r="K16">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>742</v>
+      </c>
+      <c r="B17" t="s">
+        <v>743</v>
+      </c>
+      <c r="C17" t="s">
+        <v>726</v>
+      </c>
+      <c r="D17" t="s">
+        <v>727</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>15</v>
+      </c>
+      <c r="K17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>742</v>
+      </c>
+      <c r="B18" t="s">
+        <v>743</v>
+      </c>
+      <c r="C18" t="s">
+        <v>726</v>
+      </c>
+      <c r="D18" t="s">
+        <v>727</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>30</v>
+      </c>
+      <c r="K18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>742</v>
+      </c>
+      <c r="B19" t="s">
+        <v>743</v>
+      </c>
+      <c r="C19" t="s">
+        <v>726</v>
+      </c>
+      <c r="D19" t="s">
+        <v>727</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>55</v>
+      </c>
+      <c r="K19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>742</v>
+      </c>
+      <c r="B20" t="s">
+        <v>743</v>
+      </c>
+      <c r="C20" t="s">
+        <v>726</v>
+      </c>
+      <c r="D20" t="s">
+        <v>727</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>80</v>
+      </c>
+      <c r="K20">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>742</v>
+      </c>
+      <c r="B21" t="s">
+        <v>743</v>
+      </c>
+      <c r="C21" t="s">
+        <v>726</v>
+      </c>
+      <c r="D21" t="s">
+        <v>727</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="J21">
+        <v>110</v>
+      </c>
+      <c r="K21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>742</v>
+      </c>
+      <c r="B22" t="s">
+        <v>743</v>
+      </c>
+      <c r="C22" t="s">
+        <v>726</v>
+      </c>
+      <c r="D22" t="s">
+        <v>727</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22">
+        <v>5</v>
+      </c>
+      <c r="J22">
+        <v>140</v>
+      </c>
+      <c r="K22">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>742</v>
+      </c>
+      <c r="B23" t="s">
+        <v>743</v>
+      </c>
+      <c r="C23" t="s">
+        <v>726</v>
+      </c>
+      <c r="D23" t="s">
+        <v>727</v>
+      </c>
+      <c r="G23">
+        <v>6</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+      <c r="J23">
+        <v>170</v>
+      </c>
+      <c r="K23">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>742</v>
+      </c>
+      <c r="B24" t="s">
+        <v>743</v>
+      </c>
+      <c r="C24" t="s">
+        <v>726</v>
+      </c>
+      <c r="D24" t="s">
+        <v>727</v>
+      </c>
+      <c r="G24">
+        <v>7</v>
+      </c>
+      <c r="H24">
+        <v>7</v>
+      </c>
+      <c r="J24">
+        <v>150</v>
+      </c>
+      <c r="K24">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FC969D-9D58-4E43-BD3E-79A846E161EE}">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I318"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.140625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="22.2109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="22.25" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5495,7 +6196,7 @@
       </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
@@ -5509,7 +6210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="5">
         <v>110101</v>
       </c>
@@ -5523,7 +6224,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>110102</v>
       </c>
@@ -5537,7 +6238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>110103</v>
       </c>
@@ -5551,7 +6252,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>110104</v>
       </c>
@@ -5565,7 +6266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>110105</v>
       </c>
@@ -5579,7 +6280,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>110106</v>
       </c>
@@ -5593,7 +6294,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>110107</v>
       </c>
@@ -5607,7 +6308,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>110108</v>
       </c>
@@ -5621,7 +6322,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>110109</v>
       </c>
@@ -5635,7 +6336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>110110</v>
       </c>
@@ -5649,7 +6350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>110111</v>
       </c>
@@ -5663,7 +6364,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>110112</v>
       </c>
@@ -5677,7 +6378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>110114</v>
       </c>
@@ -5691,7 +6392,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>110115</v>
       </c>
@@ -5705,7 +6406,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="8">
         <v>110116</v>
       </c>
@@ -5719,7 +6420,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="8">
         <v>110117</v>
       </c>
@@ -5733,7 +6434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="8">
         <v>110118</v>
       </c>
@@ -5747,7 +6448,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="8">
         <v>110120</v>
       </c>
@@ -5761,7 +6462,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="8">
         <v>110121</v>
       </c>
@@ -5775,7 +6476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="8">
         <v>110122</v>
       </c>
@@ -5789,7 +6490,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="8">
         <v>110124</v>
       </c>
@@ -5803,7 +6504,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>110125</v>
       </c>
@@ -5817,7 +6518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>110126</v>
       </c>
@@ -5831,7 +6532,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>110127</v>
       </c>
@@ -5845,7 +6546,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="8">
         <v>110128</v>
       </c>
@@ -5859,7 +6560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="8">
         <v>110129</v>
       </c>
@@ -5873,7 +6574,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="8">
         <v>110130</v>
       </c>
@@ -5887,7 +6588,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="8">
         <v>110131</v>
       </c>
@@ -5901,7 +6602,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="8">
         <v>110132</v>
       </c>
@@ -5915,7 +6616,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="8">
         <v>110133</v>
       </c>
@@ -5929,7 +6630,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="8">
         <v>110134</v>
       </c>
@@ -5943,7 +6644,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="8">
         <v>110135</v>
       </c>
@@ -5957,7 +6658,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="8">
         <v>110136</v>
       </c>
@@ -5971,7 +6672,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="8">
         <v>110137</v>
       </c>
@@ -5985,7 +6686,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="8">
         <v>110138</v>
       </c>
@@ -5999,7 +6700,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="8">
         <v>110139</v>
       </c>
@@ -6016,7 +6717,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="12">
         <v>110140</v>
       </c>
@@ -6033,7 +6734,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="8">
         <v>110143</v>
       </c>
@@ -6047,7 +6748,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="8">
         <v>110145</v>
       </c>
@@ -6061,7 +6762,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="8">
         <v>110146</v>
       </c>
@@ -6075,7 +6776,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="8">
         <v>110201</v>
       </c>
@@ -6089,7 +6790,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="8">
         <v>110202</v>
       </c>
@@ -6103,7 +6804,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="8">
         <v>110204</v>
       </c>
@@ -6117,7 +6818,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="8">
         <v>110301</v>
       </c>
@@ -6131,7 +6832,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="8">
         <v>110302</v>
       </c>
@@ -6145,7 +6846,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="8">
         <v>110304</v>
       </c>
@@ -6159,7 +6860,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A49" s="8">
         <v>110306</v>
       </c>
@@ -6173,7 +6874,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A50" s="8">
         <v>110308</v>
       </c>
@@ -6187,7 +6888,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A51" s="8">
         <v>110401</v>
       </c>
@@ -6201,7 +6902,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A52" s="8">
         <v>110402</v>
       </c>
@@ -6216,7 +6917,7 @@
       </c>
       <c r="I52" s="15"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A53" s="8">
         <v>110404</v>
       </c>
@@ -6231,7 +6932,7 @@
       </c>
       <c r="I53" s="15"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A54" s="8">
         <v>110405</v>
       </c>
@@ -6246,7 +6947,7 @@
       </c>
       <c r="I54" s="15"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A55" s="8">
         <v>110501</v>
       </c>
@@ -6261,7 +6962,7 @@
       </c>
       <c r="I55" s="15"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A56" s="8">
         <v>110502</v>
       </c>
@@ -6276,7 +6977,7 @@
       </c>
       <c r="I56" s="15"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A57" s="8">
         <v>110503</v>
       </c>
@@ -6291,7 +6992,7 @@
       </c>
       <c r="I57" s="15"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A58" s="8">
         <v>110504</v>
       </c>
@@ -6306,7 +7007,7 @@
       </c>
       <c r="I58" s="15"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A59" s="8">
         <v>110505</v>
       </c>
@@ -6321,7 +7022,7 @@
       </c>
       <c r="I59" s="15"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A60" s="8">
         <v>110506</v>
       </c>
@@ -6335,7 +7036,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A61" s="8">
         <v>110507</v>
       </c>
@@ -6349,7 +7050,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A62" s="8">
         <v>110508</v>
       </c>
@@ -6363,7 +7064,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A63" s="8">
         <v>110509</v>
       </c>
@@ -6377,7 +7078,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A64" s="8">
         <v>110601</v>
       </c>
@@ -6391,7 +7092,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="16">
         <v>110602</v>
       </c>
@@ -6405,7 +7106,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="8">
         <v>110603</v>
       </c>
@@ -6419,7 +7120,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="16">
         <v>110604</v>
       </c>
@@ -6433,7 +7134,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="8">
         <v>110607</v>
       </c>
@@ -6447,7 +7148,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="8">
         <v>110701</v>
       </c>
@@ -6461,7 +7162,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="8">
         <v>110702</v>
       </c>
@@ -6475,7 +7176,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="8">
         <v>110703</v>
       </c>
@@ -6489,7 +7190,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="8">
         <v>110704</v>
       </c>
@@ -6503,7 +7204,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="8">
         <v>110801</v>
       </c>
@@ -6517,7 +7218,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="8">
         <v>110802</v>
       </c>
@@ -6531,7 +7232,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="8">
         <v>110803</v>
       </c>
@@ -6545,7 +7246,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="8">
         <v>110804</v>
       </c>
@@ -6559,7 +7260,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="8">
         <v>110805</v>
       </c>
@@ -6573,7 +7274,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="8">
         <v>110806</v>
       </c>
@@ -6587,7 +7288,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="8">
         <v>110807</v>
       </c>
@@ -6601,7 +7302,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="8">
         <v>110808</v>
       </c>
@@ -6615,7 +7316,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="8">
         <v>110809</v>
       </c>
@@ -6629,7 +7330,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A82" s="18">
         <v>110810</v>
       </c>
@@ -6643,7 +7344,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="16">
         <v>120901</v>
       </c>
@@ -6657,7 +7358,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="8">
         <v>120902</v>
       </c>
@@ -6671,7 +7372,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="8">
         <v>120903</v>
       </c>
@@ -6685,7 +7386,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="8">
         <v>120904</v>
       </c>
@@ -6699,7 +7400,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="8">
         <v>120905</v>
       </c>
@@ -6713,7 +7414,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="8">
         <v>120906</v>
       </c>
@@ -6727,7 +7428,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="8">
         <v>120907</v>
       </c>
@@ -6741,7 +7442,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="8">
         <v>120908</v>
       </c>
@@ -6755,7 +7456,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="8">
         <v>120909</v>
       </c>
@@ -6769,7 +7470,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="8">
         <v>120910</v>
       </c>
@@ -6783,7 +7484,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="8">
         <v>120912</v>
       </c>
@@ -6797,7 +7498,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="8">
         <v>120915</v>
       </c>
@@ -6811,7 +7512,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="8">
         <v>120916</v>
       </c>
@@ -6825,7 +7526,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="8">
         <v>120917</v>
       </c>
@@ -6839,7 +7540,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="8">
         <v>120918</v>
       </c>
@@ -6853,7 +7554,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="8">
         <v>120919</v>
       </c>
@@ -6867,7 +7568,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="8">
         <v>121001</v>
       </c>
@@ -6881,7 +7582,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="8">
         <v>121002</v>
       </c>
@@ -6895,7 +7596,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="8">
         <v>121003</v>
       </c>
@@ -6909,7 +7610,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="8">
         <v>121004</v>
       </c>
@@ -6923,7 +7624,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="8">
         <v>121005</v>
       </c>
@@ -6937,7 +7638,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="8">
         <v>121006</v>
       </c>
@@ -6951,7 +7652,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="8">
         <v>121007</v>
       </c>
@@ -6965,7 +7666,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="8">
         <v>121008</v>
       </c>
@@ -6979,7 +7680,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="8">
         <v>121009</v>
       </c>
@@ -6993,7 +7694,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" s="8">
         <v>121010</v>
       </c>
@@ -7007,7 +7708,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="8">
         <v>121011</v>
       </c>
@@ -7021,7 +7722,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="8">
         <v>121101</v>
       </c>
@@ -7035,7 +7736,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="8">
         <v>121102</v>
       </c>
@@ -7049,7 +7750,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="16">
         <v>121103</v>
       </c>
@@ -7063,7 +7764,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A113" s="8">
         <v>121104</v>
       </c>
@@ -7077,7 +7778,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A114" s="16">
         <v>121105</v>
       </c>
@@ -7091,7 +7792,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A115" s="8">
         <v>121106</v>
       </c>
@@ -7105,7 +7806,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A116" s="16">
         <v>121107</v>
       </c>
@@ -7119,7 +7820,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A117" s="16">
         <v>121111</v>
       </c>
@@ -7133,7 +7834,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A118" s="8">
         <v>121112</v>
       </c>
@@ -7147,7 +7848,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A119" s="16">
         <v>121113</v>
       </c>
@@ -7161,7 +7862,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A120" s="8">
         <v>121114</v>
       </c>
@@ -7175,7 +7876,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A121" s="16">
         <v>121115</v>
       </c>
@@ -7189,7 +7890,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A122" s="8">
         <v>121116</v>
       </c>
@@ -7203,7 +7904,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A123" s="16">
         <v>121117</v>
       </c>
@@ -7217,7 +7918,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A124" s="8">
         <v>121201</v>
       </c>
@@ -7231,7 +7932,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A125" s="18">
         <v>121202</v>
       </c>
@@ -7245,7 +7946,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A126" s="16">
         <v>121301</v>
       </c>
@@ -7259,7 +7960,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A127" s="8">
         <v>121302</v>
       </c>
@@ -7273,7 +7974,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A128" s="8">
         <v>121303</v>
       </c>
@@ -7287,7 +7988,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A129" s="8">
         <v>121304</v>
       </c>
@@ -7301,7 +8002,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A130" s="16">
         <v>121305</v>
       </c>
@@ -7315,7 +8016,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A131" s="8">
         <v>121306</v>
       </c>
@@ -7329,7 +8030,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A132" s="8">
         <v>121307</v>
       </c>
@@ -7343,7 +8044,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A133" s="8">
         <v>121309</v>
       </c>
@@ -7357,7 +8058,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A134" s="8">
         <v>121310</v>
       </c>
@@ -7371,7 +8072,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A135" s="8">
         <v>121311</v>
       </c>
@@ -7385,7 +8086,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A136" s="8">
         <v>121317</v>
       </c>
@@ -7399,7 +8100,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A137" s="8">
         <v>121320</v>
       </c>
@@ -7413,7 +8114,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A138" s="8">
         <v>121321</v>
       </c>
@@ -7427,7 +8128,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A139" s="8">
         <v>121328</v>
       </c>
@@ -7441,7 +8142,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A140" s="8">
         <v>121329</v>
       </c>
@@ -7455,7 +8156,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A141" s="8">
         <v>121330</v>
       </c>
@@ -7469,7 +8170,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A142" s="8">
         <v>121332</v>
       </c>
@@ -7483,7 +8184,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A143" s="8">
         <v>121333</v>
       </c>
@@ -7497,7 +8198,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A144" s="8">
         <v>121401</v>
       </c>
@@ -7511,7 +8212,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A145" s="8">
         <v>121402</v>
       </c>
@@ -7525,7 +8226,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A146" s="8">
         <v>121403</v>
       </c>
@@ -7539,7 +8240,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A147" s="8">
         <v>121404</v>
       </c>
@@ -7553,7 +8254,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A148" s="8">
         <v>121405</v>
       </c>
@@ -7567,7 +8268,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A149" s="8">
         <v>131501</v>
       </c>
@@ -7581,7 +8282,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A150" s="8">
         <v>131502</v>
       </c>
@@ -7595,7 +8296,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A151" s="8">
         <v>131503</v>
       </c>
@@ -7609,7 +8310,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A152" s="8">
         <v>131504</v>
       </c>
@@ -7623,7 +8324,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A153" s="8">
         <v>131505</v>
       </c>
@@ -7637,7 +8338,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A154" s="8">
         <v>131506</v>
       </c>
@@ -7651,7 +8352,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A155" s="8">
         <v>131507</v>
       </c>
@@ -7665,7 +8366,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A156" s="8">
         <v>131508</v>
       </c>
@@ -7679,7 +8380,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A157" s="8">
         <v>131509</v>
       </c>
@@ -7693,7 +8394,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A158" s="8">
         <v>131511</v>
       </c>
@@ -7707,7 +8408,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A159" s="8">
         <v>131515</v>
       </c>
@@ -7721,7 +8422,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A160" s="8">
         <v>131519</v>
       </c>
@@ -7735,7 +8436,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A161" s="8">
         <v>131524</v>
       </c>
@@ -7749,7 +8450,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A162" s="8">
         <v>131525</v>
       </c>
@@ -7763,7 +8464,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A163" s="8">
         <v>131526</v>
       </c>
@@ -7777,7 +8478,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A164" s="8">
         <v>131527</v>
       </c>
@@ -7791,7 +8492,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A165" s="8">
         <v>131528</v>
       </c>
@@ -7805,7 +8506,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A166" s="8">
         <v>131529</v>
       </c>
@@ -7819,7 +8520,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A167" s="8">
         <v>131531</v>
       </c>
@@ -7833,7 +8534,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A168" s="8">
         <v>131534</v>
       </c>
@@ -7847,7 +8548,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A169" s="8">
         <v>131536</v>
       </c>
@@ -7861,7 +8562,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A170" s="8">
         <v>131601</v>
       </c>
@@ -7875,7 +8576,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A171" s="8">
         <v>131602</v>
       </c>
@@ -7889,7 +8590,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A172" s="5">
         <v>141801</v>
       </c>
@@ -7903,7 +8604,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A173" s="8">
         <v>141802</v>
       </c>
@@ -7917,7 +8618,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A174" s="8">
         <v>141803</v>
       </c>
@@ -7931,7 +8632,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A175" s="8">
         <v>141804</v>
       </c>
@@ -7945,7 +8646,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A176" s="8">
         <v>141806</v>
       </c>
@@ -7959,7 +8660,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A177" s="8">
         <v>141807</v>
       </c>
@@ -7973,7 +8674,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A178" s="8">
         <v>141808</v>
       </c>
@@ -7987,7 +8688,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A179" s="8">
         <v>141809</v>
       </c>
@@ -8001,7 +8702,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A180" s="8">
         <v>141810</v>
       </c>
@@ -8015,7 +8716,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A181" s="8">
         <v>141811</v>
       </c>
@@ -8029,7 +8730,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A182" s="8">
         <v>141812</v>
       </c>
@@ -8043,7 +8744,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A183" s="8">
         <v>141901</v>
       </c>
@@ -8057,7 +8758,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A184" s="8">
         <v>141902</v>
       </c>
@@ -8071,7 +8772,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A185" s="8">
         <v>141903</v>
       </c>
@@ -8085,7 +8786,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A186" s="8">
         <v>141904</v>
       </c>
@@ -8099,7 +8800,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A187" s="8">
         <v>141905</v>
       </c>
@@ -8113,7 +8814,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A188" s="8">
         <v>141906</v>
       </c>
@@ -8127,7 +8828,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A189" s="8">
         <v>141907</v>
       </c>
@@ -8141,7 +8842,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A190" s="8">
         <v>141908</v>
       </c>
@@ -8155,7 +8856,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A191" s="8">
         <v>142001</v>
       </c>
@@ -8169,7 +8870,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A192" s="8">
         <v>142002</v>
       </c>
@@ -8183,7 +8884,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A193" s="8">
         <v>142101</v>
       </c>
@@ -8197,7 +8898,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A194" s="8">
         <v>142102</v>
       </c>
@@ -8211,7 +8912,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A195" s="8">
         <v>142103</v>
       </c>
@@ -8225,7 +8926,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A196" s="8">
         <v>142104</v>
       </c>
@@ -8239,7 +8940,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A197" s="8">
         <v>142105</v>
       </c>
@@ -8253,7 +8954,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A198" s="8">
         <v>142106</v>
       </c>
@@ -8267,7 +8968,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A199" s="8">
         <v>142107</v>
       </c>
@@ -8281,7 +8982,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A200" s="8">
         <v>142108</v>
       </c>
@@ -8295,7 +8996,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A201" s="8">
         <v>142109</v>
       </c>
@@ -8309,7 +9010,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A202" s="8">
         <v>142201</v>
       </c>
@@ -8323,7 +9024,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <v>142203</v>
       </c>
@@ -8337,7 +9038,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A204" s="5">
         <v>152301</v>
       </c>
@@ -8351,7 +9052,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A205" s="8">
         <v>152302</v>
       </c>
@@ -8365,7 +9066,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A206" s="8">
         <v>152304</v>
       </c>
@@ -8382,7 +9083,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A207" s="8">
         <v>152305</v>
       </c>
@@ -8396,7 +9097,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A208" s="8">
         <v>152306</v>
       </c>
@@ -8410,7 +9111,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A209" s="12">
         <v>152307</v>
       </c>
@@ -8427,7 +9128,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A210" s="8">
         <v>152309</v>
       </c>
@@ -8441,7 +9142,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A211" s="8">
         <v>152310</v>
       </c>
@@ -8455,7 +9156,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A212" s="8">
         <v>152312</v>
       </c>
@@ -8469,7 +9170,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A213" s="8">
         <v>152315</v>
       </c>
@@ -8483,7 +9184,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A214" s="8">
         <v>152316</v>
       </c>
@@ -8497,7 +9198,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A215" s="8">
         <v>152318</v>
       </c>
@@ -8511,7 +9212,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A216" s="8">
         <v>152322</v>
       </c>
@@ -8525,7 +9226,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A217" s="8">
         <v>152401</v>
       </c>
@@ -8539,7 +9240,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A218" s="8">
         <v>152404</v>
       </c>
@@ -8553,7 +9254,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A219" s="8">
         <v>152501</v>
       </c>
@@ -8567,7 +9268,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A220" s="8">
         <v>152506</v>
       </c>
@@ -8581,7 +9282,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A221" s="8">
         <v>152511</v>
       </c>
@@ -8595,7 +9296,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A222" s="8">
         <v>152512</v>
       </c>
@@ -8609,7 +9310,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A223" s="18">
         <v>152601</v>
       </c>
@@ -8623,7 +9324,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A224" s="5">
         <v>162701</v>
       </c>
@@ -8637,7 +9338,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A225" s="8">
         <v>162702</v>
       </c>
@@ -8651,7 +9352,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A226" s="8">
         <v>162703</v>
       </c>
@@ -8665,7 +9366,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A227" s="8">
         <v>162704</v>
       </c>
@@ -8679,7 +9380,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A228" s="8">
         <v>162705</v>
       </c>
@@ -8693,7 +9394,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A229" s="8">
         <v>162706</v>
       </c>
@@ -8707,7 +9408,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A230" s="8">
         <v>162707</v>
       </c>
@@ -8721,7 +9422,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A231" s="8">
         <v>162708</v>
       </c>
@@ -8735,7 +9436,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A232" s="8">
         <v>162709</v>
       </c>
@@ -8749,7 +9450,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A233" s="8">
         <v>162710</v>
       </c>
@@ -8763,7 +9464,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A234" s="8">
         <v>162711</v>
       </c>
@@ -8777,7 +9478,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A235" s="8">
         <v>162713</v>
       </c>
@@ -8794,7 +9495,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A236" s="12">
         <v>162716</v>
       </c>
@@ -8811,7 +9512,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A237" s="8">
         <v>162801</v>
       </c>
@@ -8825,7 +9526,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A238" s="8">
         <v>162802</v>
       </c>
@@ -8839,7 +9540,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A239" s="8">
         <v>162804</v>
       </c>
@@ -8853,7 +9554,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A240" s="8">
         <v>162805</v>
       </c>
@@ -8867,7 +9568,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A241" s="8">
         <v>162806</v>
       </c>
@@ -8884,7 +9585,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A242" s="12">
         <v>162807</v>
       </c>
@@ -8901,7 +9602,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A243" s="12">
         <v>162808</v>
       </c>
@@ -8918,7 +9619,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A244" s="8">
         <v>162901</v>
       </c>
@@ -8932,7 +9633,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A245" s="8">
         <v>163001</v>
       </c>
@@ -8946,7 +9647,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A246" s="8">
         <v>163101</v>
       </c>
@@ -8960,7 +9661,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A247" s="8">
         <v>163102</v>
       </c>
@@ -8974,7 +9675,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A248" s="8">
         <v>163103</v>
       </c>
@@ -8988,7 +9689,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A249" s="8">
         <v>163104</v>
       </c>
@@ -9002,7 +9703,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A250" s="8">
         <v>163105</v>
       </c>
@@ -9016,7 +9717,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A251" s="8">
         <v>163106</v>
       </c>
@@ -9030,7 +9731,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A252" s="8">
         <v>163107</v>
       </c>
@@ -9044,7 +9745,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A253" s="8">
         <v>163108</v>
       </c>
@@ -9058,7 +9759,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A254" s="8">
         <v>163201</v>
       </c>
@@ -9072,7 +9773,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A255" s="8">
         <v>163203</v>
       </c>
@@ -9086,7 +9787,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A256" s="8">
         <v>163206</v>
       </c>
@@ -9100,7 +9801,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A257" s="8">
         <v>163301</v>
       </c>
@@ -9114,7 +9815,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A258" s="8">
         <v>163303</v>
       </c>
@@ -9128,7 +9829,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A259" s="8">
         <v>163304</v>
       </c>
@@ -9142,7 +9843,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A260" s="18">
         <v>163406</v>
       </c>
@@ -9156,7 +9857,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="261" spans="1:4" s="24" customFormat="1" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" s="24" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A261" s="21">
         <v>170202</v>
       </c>
@@ -9170,7 +9871,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="262" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A262" s="25">
         <v>170203</v>
       </c>
@@ -9184,7 +9885,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="263" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A263" s="28">
         <v>170204</v>
       </c>
@@ -9198,7 +9899,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="264" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A264" s="28">
         <v>170205</v>
       </c>
@@ -9212,7 +9913,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="265" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A265" s="28">
         <v>170206</v>
       </c>
@@ -9226,7 +9927,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="266" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A266" s="28">
         <v>170207</v>
       </c>
@@ -9240,7 +9941,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="267" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A267" s="28">
         <v>170208</v>
       </c>
@@ -9254,7 +9955,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="268" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A268" s="28">
         <v>170209</v>
       </c>
@@ -9268,7 +9969,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="269" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A269" s="28">
         <v>170210</v>
       </c>
@@ -9282,7 +9983,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="270" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A270" s="28">
         <v>170211</v>
       </c>
@@ -9296,7 +9997,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="271" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A271" s="28">
         <v>170212</v>
       </c>
@@ -9310,7 +10011,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="272" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A272" s="28">
         <v>170213</v>
       </c>
@@ -9324,7 +10025,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="273" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A273" s="28">
         <v>170214</v>
       </c>
@@ -9338,7 +10039,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="274" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A274" s="28">
         <v>170215</v>
       </c>
@@ -9352,7 +10053,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="275" spans="1:5" s="24" customFormat="1" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" s="24" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A275" s="31">
         <v>170216</v>
       </c>
@@ -9369,7 +10070,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A276" s="34">
         <v>177777</v>
       </c>
@@ -9383,7 +10084,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A277" s="36">
         <v>180001</v>
       </c>
@@ -9397,7 +10098,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A278" s="5">
         <v>90001</v>
       </c>
@@ -9411,7 +10112,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A279" s="8">
         <v>90002</v>
       </c>
@@ -9425,7 +10126,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A280" s="8">
         <v>90003</v>
       </c>
@@ -9439,7 +10140,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A281" s="8">
         <v>90004</v>
       </c>
@@ -9453,7 +10154,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A282" s="8">
         <v>90005</v>
       </c>
@@ -9467,7 +10168,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A283" s="8">
         <v>90006</v>
       </c>
@@ -9481,7 +10182,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A284" s="8">
         <v>90007</v>
       </c>
@@ -9495,7 +10196,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A285" s="8">
         <v>90008</v>
       </c>
@@ -9509,7 +10210,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A286" s="8">
         <v>90009</v>
       </c>
@@ -9523,7 +10224,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A287" s="8">
         <v>90010</v>
       </c>
@@ -9537,7 +10238,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A288" s="8">
         <v>90011</v>
       </c>
@@ -9551,7 +10252,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A289" s="8">
         <v>90012</v>
       </c>
@@ -9565,7 +10266,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A290" s="8">
         <v>90013</v>
       </c>
@@ -9579,7 +10280,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A291" s="8">
         <v>90014</v>
       </c>
@@ -9593,7 +10294,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A292" s="8">
         <v>90015</v>
       </c>
@@ -9607,7 +10308,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A293" s="8">
         <v>90016</v>
       </c>
@@ -9621,7 +10322,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A294" s="8">
         <v>90017</v>
       </c>
@@ -9635,7 +10336,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A295" s="8">
         <v>90018</v>
       </c>
@@ -9649,7 +10350,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A296" s="8">
         <v>90019</v>
       </c>
@@ -9663,7 +10364,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A297" s="8">
         <v>90020</v>
       </c>
@@ -9677,7 +10378,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A298" s="8">
         <v>90021</v>
       </c>
@@ -9691,7 +10392,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A299" s="8">
         <v>90022</v>
       </c>
@@ -9705,7 +10406,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A300" s="8">
         <v>90023</v>
       </c>
@@ -9719,7 +10420,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A301" s="8">
         <v>90024</v>
       </c>
@@ -9733,7 +10434,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A302" s="8">
         <v>90025</v>
       </c>
@@ -9747,7 +10448,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A303" s="8">
         <v>90026</v>
       </c>
@@ -9761,7 +10462,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A304" s="8">
         <v>90027</v>
       </c>
@@ -9775,7 +10476,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A305" s="8">
         <v>90028</v>
       </c>
@@ -9789,7 +10490,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A306" s="8">
         <v>90029</v>
       </c>
@@ -9803,7 +10504,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A307" s="8">
         <v>90030</v>
       </c>
@@ -9817,7 +10518,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A308" s="8">
         <v>90031</v>
       </c>
@@ -9831,7 +10532,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A309" s="8">
         <v>90032</v>
       </c>
@@ -9845,7 +10546,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A310" s="8">
         <v>90033</v>
       </c>
@@ -9859,7 +10560,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A311" s="8">
         <v>90034</v>
       </c>
@@ -9873,7 +10574,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A312" s="8">
         <v>90035</v>
       </c>
@@ -9887,7 +10588,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A313" s="8">
         <v>90036</v>
       </c>
@@ -9901,7 +10602,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A314" s="8">
         <v>90037</v>
       </c>
@@ -9915,7 +10616,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A315" s="8">
         <v>90038</v>
       </c>
@@ -9929,7 +10630,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A316" s="8">
         <v>90039</v>
       </c>
@@ -9943,7 +10644,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A317" s="8">
         <v>90040</v>
       </c>
@@ -9957,7 +10658,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A318" s="72">
         <v>999999</v>
       </c>
@@ -9981,24 +10682,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3F87FA4-8AE3-4E4F-AF33-D2B7AA208BA0}">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E204"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.2109375" style="41" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="41" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="42" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="68" customWidth="1"/>
-    <col min="5" max="5" width="34.140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.125" style="41" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
@@ -10007,7 +10708,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="89" t="s">
         <v>1</v>
       </c>
@@ -10021,7 +10722,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="46">
         <v>210101</v>
       </c>
@@ -10035,7 +10736,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="48">
         <v>210102</v>
       </c>
@@ -10049,7 +10750,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="48">
         <v>210103</v>
       </c>
@@ -10063,7 +10764,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="48">
         <v>210104</v>
       </c>
@@ -10077,7 +10778,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="48">
         <v>210105</v>
       </c>
@@ -10091,7 +10792,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="48">
         <v>210106</v>
       </c>
@@ -10105,7 +10806,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="48">
         <v>210107</v>
       </c>
@@ -10119,7 +10820,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="48">
         <v>210108</v>
       </c>
@@ -10133,7 +10834,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="48">
         <v>210109</v>
       </c>
@@ -10147,7 +10848,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="48">
         <v>210110</v>
       </c>
@@ -10161,7 +10862,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="48">
         <v>210112</v>
       </c>
@@ -10175,7 +10876,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="48">
         <v>210113</v>
       </c>
@@ -10189,7 +10890,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="48">
         <v>210114</v>
       </c>
@@ -10203,7 +10904,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="48">
         <v>210115</v>
       </c>
@@ -10217,7 +10918,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="48">
         <v>210116</v>
       </c>
@@ -10231,7 +10932,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="48">
         <v>210117</v>
       </c>
@@ -10245,7 +10946,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="48">
         <v>210118</v>
       </c>
@@ -10259,7 +10960,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="48">
         <v>210119</v>
       </c>
@@ -10273,7 +10974,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="48">
         <v>210120</v>
       </c>
@@ -10290,7 +10991,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="50">
         <v>210121</v>
       </c>
@@ -10307,7 +11008,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="48">
         <v>210123</v>
       </c>
@@ -10321,7 +11022,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="52">
         <v>210124</v>
       </c>
@@ -10335,7 +11036,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="48">
         <v>210125</v>
       </c>
@@ -10349,7 +11050,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="48">
         <v>210201</v>
       </c>
@@ -10363,7 +11064,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="48">
         <v>210202</v>
       </c>
@@ -10377,7 +11078,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="48">
         <v>210204</v>
       </c>
@@ -10391,7 +11092,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="48">
         <v>210301</v>
       </c>
@@ -10405,7 +11106,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="48">
         <v>210401</v>
       </c>
@@ -10419,7 +11120,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="48">
         <v>210402</v>
       </c>
@@ -10433,7 +11134,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="48">
         <v>210403</v>
       </c>
@@ -10447,7 +11148,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="48">
         <v>210501</v>
       </c>
@@ -10461,7 +11162,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="48">
         <v>210502</v>
       </c>
@@ -10475,7 +11176,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="48">
         <v>210503</v>
       </c>
@@ -10489,7 +11190,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="48">
         <v>210504</v>
       </c>
@@ -10503,7 +11204,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="48">
         <v>210505</v>
       </c>
@@ -10517,7 +11218,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="48">
         <v>210506</v>
       </c>
@@ -10531,7 +11232,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="48">
         <v>210601</v>
       </c>
@@ -10545,7 +11246,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="48">
         <v>210602</v>
       </c>
@@ -10559,7 +11260,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="48">
         <v>210603</v>
       </c>
@@ -10573,7 +11274,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="48">
         <v>210701</v>
       </c>
@@ -10587,7 +11288,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="48">
         <v>210702</v>
       </c>
@@ -10601,7 +11302,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="52">
         <v>210801</v>
       </c>
@@ -10615,7 +11316,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="48">
         <v>210802</v>
       </c>
@@ -10629,7 +11330,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="48">
         <v>210803</v>
       </c>
@@ -10643,7 +11344,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="54">
         <v>210804</v>
       </c>
@@ -10657,7 +11358,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="52">
         <v>220901</v>
       </c>
@@ -10671,7 +11372,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="48">
         <v>220902</v>
       </c>
@@ -10685,7 +11386,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" s="48">
         <v>220903</v>
       </c>
@@ -10699,7 +11400,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A51" s="48">
         <v>220904</v>
       </c>
@@ -10713,7 +11414,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A52" s="48">
         <v>220905</v>
       </c>
@@ -10727,7 +11428,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" s="48">
         <v>220906</v>
       </c>
@@ -10741,7 +11442,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" s="48">
         <v>220907</v>
       </c>
@@ -10755,7 +11456,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" s="48">
         <v>220908</v>
       </c>
@@ -10769,7 +11470,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" s="48">
         <v>220909</v>
       </c>
@@ -10783,7 +11484,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="48">
         <v>220910</v>
       </c>
@@ -10797,7 +11498,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" s="48">
         <v>220911</v>
       </c>
@@ -10811,7 +11512,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="48">
         <v>221001</v>
       </c>
@@ -10825,7 +11526,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" s="48">
         <v>221002</v>
       </c>
@@ -10839,7 +11540,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" s="48">
         <v>221003</v>
       </c>
@@ -10853,7 +11554,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A62" s="48">
         <v>221101</v>
       </c>
@@ -10867,7 +11568,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="48">
         <v>221102</v>
       </c>
@@ -10884,7 +11585,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="50">
         <v>221103</v>
       </c>
@@ -10901,7 +11602,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="48">
         <v>221104</v>
       </c>
@@ -10915,7 +11616,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="48">
         <v>221105</v>
       </c>
@@ -10929,7 +11630,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="48">
         <v>221106</v>
       </c>
@@ -10943,7 +11644,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="48">
         <v>221107</v>
       </c>
@@ -10957,7 +11658,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="48">
         <v>221108</v>
       </c>
@@ -10971,7 +11672,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="48">
         <v>221109</v>
       </c>
@@ -10985,7 +11686,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="52">
         <v>221201</v>
       </c>
@@ -10999,7 +11700,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A72" s="54">
         <v>221202</v>
       </c>
@@ -11013,7 +11714,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="52">
         <v>231301</v>
       </c>
@@ -11027,7 +11728,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="48">
         <v>231302</v>
       </c>
@@ -11041,7 +11742,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="48">
         <v>231303</v>
       </c>
@@ -11055,7 +11756,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="48">
         <v>231304</v>
       </c>
@@ -11069,7 +11770,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="48">
         <v>231307</v>
       </c>
@@ -11083,7 +11784,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="48">
         <v>231308</v>
       </c>
@@ -11097,7 +11798,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="48">
         <v>231309</v>
       </c>
@@ -11111,7 +11812,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="48">
         <v>231401</v>
       </c>
@@ -11125,7 +11826,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="48">
         <v>231501</v>
       </c>
@@ -11139,7 +11840,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="48">
         <v>231502</v>
       </c>
@@ -11153,7 +11854,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="48">
         <v>231504</v>
       </c>
@@ -11167,7 +11868,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="48">
         <v>231505</v>
       </c>
@@ -11181,7 +11882,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="48">
         <v>231506</v>
       </c>
@@ -11195,7 +11896,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="48">
         <v>231507</v>
       </c>
@@ -11209,7 +11910,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="48">
         <v>231509</v>
       </c>
@@ -11223,7 +11924,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="48">
         <v>231510</v>
       </c>
@@ -11237,7 +11938,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="48">
         <v>231511</v>
       </c>
@@ -11251,7 +11952,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="48">
         <v>231513</v>
       </c>
@@ -11265,7 +11966,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="48">
         <v>231516</v>
       </c>
@@ -11279,7 +11980,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="48">
         <v>231517</v>
       </c>
@@ -11293,7 +11994,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="48">
         <v>231518</v>
       </c>
@@ -11307,7 +12008,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="48">
         <v>231519</v>
       </c>
@@ -11321,7 +12022,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A95" s="54">
         <v>231601</v>
       </c>
@@ -11335,7 +12036,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="52">
         <v>241801</v>
       </c>
@@ -11349,7 +12050,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="48">
         <v>241802</v>
       </c>
@@ -11363,7 +12064,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="48">
         <v>241804</v>
       </c>
@@ -11377,7 +12078,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="48">
         <v>241901</v>
       </c>
@@ -11391,7 +12092,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="48">
         <v>241903</v>
       </c>
@@ -11405,7 +12106,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="48">
         <v>242001</v>
       </c>
@@ -11419,7 +12120,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="48">
         <v>242101</v>
       </c>
@@ -11433,7 +12134,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="48">
         <v>242102</v>
       </c>
@@ -11447,7 +12148,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="48">
         <v>242103</v>
       </c>
@@ -11461,7 +12162,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="48">
         <v>242104</v>
       </c>
@@ -11475,7 +12176,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="48">
         <v>242105</v>
       </c>
@@ -11489,7 +12190,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="48">
         <v>242201</v>
       </c>
@@ -11503,7 +12204,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A108" s="54">
         <v>242202</v>
       </c>
@@ -11517,7 +12218,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="52">
         <v>252301</v>
       </c>
@@ -11531,7 +12232,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="48">
         <v>252302</v>
       </c>
@@ -11545,7 +12246,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="48">
         <v>252303</v>
       </c>
@@ -11559,7 +12260,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="48">
         <v>252304</v>
       </c>
@@ -11573,7 +12274,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A113" s="48">
         <v>252305</v>
       </c>
@@ -11587,7 +12288,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A114" s="48">
         <v>252306</v>
       </c>
@@ -11601,7 +12302,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A115" s="48">
         <v>252307</v>
       </c>
@@ -11615,7 +12316,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A116" s="48">
         <v>252308</v>
       </c>
@@ -11629,7 +12330,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A117" s="48">
         <v>252309</v>
       </c>
@@ -11643,7 +12344,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A118" s="48">
         <v>252310</v>
       </c>
@@ -11657,7 +12358,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A119" s="48">
         <v>252311</v>
       </c>
@@ -11671,7 +12372,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A120" s="48">
         <v>252402</v>
       </c>
@@ -11685,7 +12386,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A121" s="48">
         <v>252501</v>
       </c>
@@ -11699,7 +12400,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A122" s="48">
         <v>252503</v>
       </c>
@@ -11713,7 +12414,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A123" s="48">
         <v>252505</v>
       </c>
@@ -11727,7 +12428,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A124" s="56">
         <v>252601</v>
       </c>
@@ -11741,7 +12442,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A125" s="52">
         <v>262701</v>
       </c>
@@ -11758,7 +12459,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A126" s="48">
         <v>262702</v>
       </c>
@@ -11775,7 +12476,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A127" s="50">
         <v>262703</v>
       </c>
@@ -11792,7 +12493,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A128" s="50">
         <v>262704</v>
       </c>
@@ -11809,7 +12510,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A129" s="50">
         <v>262705</v>
       </c>
@@ -11826,7 +12527,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A130" s="48">
         <v>262706</v>
       </c>
@@ -11840,7 +12541,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A131" s="50">
         <v>262707</v>
       </c>
@@ -11857,7 +12558,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A132" s="48">
         <v>262709</v>
       </c>
@@ -11871,7 +12572,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A133" s="48">
         <v>262801</v>
       </c>
@@ -11885,7 +12586,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A134" s="48">
         <v>262901</v>
       </c>
@@ -11899,7 +12600,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A135" s="48">
         <v>263001</v>
       </c>
@@ -11913,7 +12614,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A136" s="48">
         <v>263003</v>
       </c>
@@ -11927,7 +12628,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A137" s="48">
         <v>263004</v>
       </c>
@@ -11941,7 +12642,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A138" s="48">
         <v>263101</v>
       </c>
@@ -11955,7 +12656,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A139" s="48">
         <v>263103</v>
       </c>
@@ -11969,7 +12670,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A140" s="48">
         <v>263104</v>
       </c>
@@ -11983,7 +12684,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A141" s="48">
         <v>263201</v>
       </c>
@@ -11997,7 +12698,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A142" s="48">
         <v>263301</v>
       </c>
@@ -12011,7 +12712,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A143" s="48">
         <v>263401</v>
       </c>
@@ -12025,7 +12726,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A144" s="58">
         <v>263404</v>
       </c>
@@ -12039,7 +12740,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A145" s="44">
         <v>270001</v>
       </c>
@@ -12053,7 +12754,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A146" s="44">
         <v>270202</v>
       </c>
@@ -12067,7 +12768,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A147" s="46">
         <v>270203</v>
       </c>
@@ -12081,7 +12782,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A148" s="48">
         <v>270204</v>
       </c>
@@ -12095,7 +12796,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A149" s="48">
         <v>270205</v>
       </c>
@@ -12109,7 +12810,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A150" s="48">
         <v>270206</v>
       </c>
@@ -12123,7 +12824,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A151" s="48">
         <v>270207</v>
       </c>
@@ -12137,7 +12838,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A152" s="48">
         <v>270208</v>
       </c>
@@ -12151,7 +12852,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A153" s="48">
         <v>270209</v>
       </c>
@@ -12165,7 +12866,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A154" s="48">
         <v>270210</v>
       </c>
@@ -12179,7 +12880,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A155" s="48">
         <v>270211</v>
       </c>
@@ -12193,7 +12894,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A156" s="48">
         <v>270212</v>
       </c>
@@ -12207,7 +12908,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A157" s="48">
         <v>270213</v>
       </c>
@@ -12221,7 +12922,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A158" s="48">
         <v>270214</v>
       </c>
@@ -12235,7 +12936,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A159" s="48">
         <v>270215</v>
       </c>
@@ -12249,7 +12950,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A160" s="60">
         <v>270216</v>
       </c>
@@ -12266,7 +12967,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A161" s="61">
         <v>280001</v>
       </c>
@@ -12280,7 +12981,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="162" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A162" s="63">
         <v>90001</v>
       </c>
@@ -12294,7 +12995,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="163" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A163" s="66">
         <v>90002</v>
       </c>
@@ -12308,7 +13009,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="164" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A164" s="66">
         <v>90003</v>
       </c>
@@ -12322,7 +13023,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="165" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A165" s="66">
         <v>90004</v>
       </c>
@@ -12336,7 +13037,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="166" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A166" s="66">
         <v>90005</v>
       </c>
@@ -12350,7 +13051,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="167" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A167" s="66">
         <v>90006</v>
       </c>
@@ -12364,7 +13065,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="168" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A168" s="66">
         <v>90007</v>
       </c>
@@ -12378,7 +13079,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="169" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A169" s="66">
         <v>90008</v>
       </c>
@@ -12392,7 +13093,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="170" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A170" s="66">
         <v>90009</v>
       </c>
@@ -12406,7 +13107,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="171" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A171" s="66">
         <v>90010</v>
       </c>
@@ -12420,7 +13121,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="172" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A172" s="66">
         <v>90011</v>
       </c>
@@ -12434,7 +13135,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="173" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A173" s="66">
         <v>90012</v>
       </c>
@@ -12448,7 +13149,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="174" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A174" s="66">
         <v>90013</v>
       </c>
@@ -12462,7 +13163,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="175" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A175" s="66">
         <v>90014</v>
       </c>
@@ -12476,7 +13177,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="176" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A176" s="66">
         <v>90015</v>
       </c>
@@ -12490,7 +13191,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="177" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A177" s="66">
         <v>90016</v>
       </c>
@@ -12504,7 +13205,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="178" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A178" s="66">
         <v>90017</v>
       </c>
@@ -12518,7 +13219,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="179" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A179" s="66">
         <v>90018</v>
       </c>
@@ -12532,7 +13233,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="180" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A180" s="66">
         <v>90019</v>
       </c>
@@ -12546,7 +13247,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="181" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A181" s="66">
         <v>90020</v>
       </c>
@@ -12560,7 +13261,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="182" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A182" s="66">
         <v>90021</v>
       </c>
@@ -12574,7 +13275,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="183" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A183" s="66">
         <v>90022</v>
       </c>
@@ -12588,7 +13289,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A184" s="66">
         <v>90023</v>
       </c>
@@ -12602,7 +13303,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="185" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A185" s="66">
         <v>90024</v>
       </c>
@@ -12616,7 +13317,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="186" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A186" s="66">
         <v>90025</v>
       </c>
@@ -12630,7 +13331,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="187" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A187" s="66">
         <v>90026</v>
       </c>
@@ -12644,7 +13345,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="188" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A188" s="66">
         <v>90027</v>
       </c>
@@ -12658,7 +13359,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="189" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A189" s="66">
         <v>90028</v>
       </c>
@@ -12672,7 +13373,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="190" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A190" s="66">
         <v>90029</v>
       </c>
@@ -12686,7 +13387,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="191" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A191" s="66">
         <v>90030</v>
       </c>
@@ -12700,7 +13401,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="192" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A192" s="66">
         <v>90031</v>
       </c>
@@ -12714,7 +13415,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="193" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A193" s="66">
         <v>90032</v>
       </c>
@@ -12728,7 +13429,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="194" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A194" s="66">
         <v>90033</v>
       </c>
@@ -12742,7 +13443,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="195" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A195" s="66">
         <v>90034</v>
       </c>
@@ -12756,7 +13457,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="196" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A196" s="66">
         <v>90035</v>
       </c>
@@ -12770,7 +13471,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="197" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A197" s="66">
         <v>90036</v>
       </c>
@@ -12784,7 +13485,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="198" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A198" s="66">
         <v>90037</v>
       </c>
@@ -12798,7 +13499,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="199" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A199" s="66">
         <v>90038</v>
       </c>
@@ -12812,7 +13513,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="200" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A200" s="66">
         <v>90039</v>
       </c>
@@ -12826,7 +13527,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="201" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A201" s="66">
         <v>90040</v>
       </c>
@@ -12840,7 +13541,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A202" s="58">
         <v>999999</v>
       </c>
@@ -12854,7 +13555,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A204" s="42"/>
     </row>
   </sheetData>

--- a/R8_県学調_問題マスタ.xlsx
+++ b/R8_県学調_問題マスタ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52852236-5613-49CD-BF73-FA596432BFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7924946-B643-451E-8DC7-F6055AB21B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2055" yWindow="1395" windowWidth="23115" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="問題マスタ" sheetId="6" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="748">
   <si>
     <t>学校コード一覧表</t>
     <rPh sb="0" eb="2">
@@ -3084,6 +3084,45 @@
   </si>
   <si>
     <t>\frac{7}{4}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> title</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>調査名</t>
+    <rPh sb="0" eb="3">
+      <t>チョウサメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>令和8年度岩手県小学校学習定着度調査　国語</t>
+    <rPh sb="0" eb="2">
+      <t>レイワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ネンド</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>イワテケン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ショウガッコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>テイチャクド</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コクゴ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4212,8 +4251,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7861881-F35C-4F9F-83E7-28DEA30120B9}" name="テーブル5" displayName="テーブル5" ref="A1:L24" totalsRowShown="0">
-  <autoFilter ref="A1:L24" xr:uid="{E7861881-F35C-4F9F-83E7-28DEA30120B9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7861881-F35C-4F9F-83E7-28DEA30120B9}" name="テーブル5" displayName="テーブル5" ref="A1:L25" totalsRowShown="0">
+  <autoFilter ref="A1:L25" xr:uid="{E7861881-F35C-4F9F-83E7-28DEA30120B9}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{4FBC1E99-EAAC-4C62-8637-41F045BE22DF}" name="データ種別"/>
     <tableColumn id="2" xr3:uid="{F474E028-1DCA-4D5D-A7D9-1EA8C1A73AAC}" name="項目"/>
@@ -5586,7 +5625,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D793BDE-8574-4356-BF6F-65AC154CE378}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -6158,6 +6197,17 @@
       </c>
       <c r="K24">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>745</v>
+      </c>
+      <c r="B25" t="s">
+        <v>746</v>
+      </c>
+      <c r="I25" t="s">
+        <v>747</v>
       </c>
     </row>
   </sheetData>

--- a/R8_県学調_問題マスタ.xlsx
+++ b/R8_県学調_問題マスタ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7924946-B643-451E-8DC7-F6055AB21B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372AE3C0-BE48-4749-81E7-BE48B1D752D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="1395" windowWidth="23115" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25425" yWindow="1890" windowWidth="23115" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="問題マスタ" sheetId="6" r:id="rId1"/>
@@ -5806,7 +5806,7 @@
         <v>727</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">

--- a/R8_県学調_問題マスタ.xlsx
+++ b/R8_県学調_問題マスタ.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9149d06814ece6b4/github/survey-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372AE3C0-BE48-4749-81E7-BE48B1D752D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{372AE3C0-BE48-4749-81E7-BE48B1D752D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AF7F832-E014-4D37-BA8F-D82107D8757D}"/>
   <bookViews>
-    <workbookView xWindow="25425" yWindow="1890" windowWidth="23115" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="問題マスタ" sheetId="6" r:id="rId1"/>
@@ -4561,20 +4561,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731ACD8B-3F3F-4FB8-AC79-3009D1AB82F2}">
   <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="2" max="3" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.25" customWidth="1"/>
+    <col min="2" max="3" width="10.2109375" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.2109375" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.875" customWidth="1"/>
-    <col min="12" max="12" width="19.875" customWidth="1"/>
-    <col min="13" max="13" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="10.25" customWidth="1"/>
+    <col min="10" max="11" width="16.85546875" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.2109375" customWidth="1"/>
+    <col min="16" max="16" width="10.2109375" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>655</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>566</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>580</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>588</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>596</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>601</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>608</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>613</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>619</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>625</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>630</v>
       </c>
@@ -5187,7 +5187,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A12" t="s">
         <v>636</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A13" t="s">
         <v>646</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A14" t="s">
         <v>650</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.65">
       <c r="A15" t="s">
         <v>654</v>
       </c>
@@ -5372,16 +5372,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33C08DAF-9E90-4F71-B777-114760BC3106}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="9.875" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
     <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="15.640625" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="9" max="9" width="51.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="51.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>681</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>712</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>712</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>712</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>712</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>713</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>713</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>713</v>
       </c>
@@ -5626,16 +5626,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D793BDE-8574-4356-BF6F-65AC154CE378}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
-    <col min="3" max="3" width="12.125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.2109375" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>714</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>724</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>724</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>724</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>724</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>724</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>724</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>724</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>724</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>735</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>735</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A12" t="s">
         <v>735</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A13" t="s">
         <v>735</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A14" t="s">
         <v>735</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A15" t="s">
         <v>735</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A16" t="s">
         <v>735</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.65">
       <c r="A17" t="s">
         <v>742</v>
       </c>
@@ -6017,7 +6017,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.65">
       <c r="A18" t="s">
         <v>742</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.65">
       <c r="A19" t="s">
         <v>742</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.65">
       <c r="A20" t="s">
         <v>742</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.65">
       <c r="A21" t="s">
         <v>742</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.65">
       <c r="A22" t="s">
         <v>742</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.65">
       <c r="A23" t="s">
         <v>742</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.65">
       <c r="A24" t="s">
         <v>742</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.65">
       <c r="A25" t="s">
         <v>745</v>
       </c>
@@ -6227,17 +6227,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I318"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="22.2109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>110101</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>110102</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>110103</v>
       </c>
@@ -6302,7 +6302,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>110104</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>110105</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>110106</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>110107</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>110108</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>110109</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>110110</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>110111</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>110112</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>110114</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>110115</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>110116</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>110117</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>110118</v>
       </c>
@@ -6498,7 +6498,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>110120</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>110121</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>110122</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>110124</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>110125</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>110126</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>110127</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>110128</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>110129</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>110130</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>110131</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>110132</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>110133</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>110134</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>110135</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>110136</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>110137</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>110138</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>110139</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>110140</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>110143</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>110145</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>110146</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>110201</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>110202</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>110204</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>110301</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>110302</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>110304</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>110306</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>110308</v>
       </c>
@@ -6938,7 +6938,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>110401</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>110402</v>
       </c>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="I52" s="15"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>110404</v>
       </c>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="I53" s="15"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>110405</v>
       </c>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="I54" s="15"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>110501</v>
       </c>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="I55" s="15"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>110502</v>
       </c>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I56" s="15"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>110503</v>
       </c>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="I57" s="15"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>110504</v>
       </c>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="I58" s="15"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>110505</v>
       </c>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="I59" s="15"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>110506</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>110507</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>110508</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>110509</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <v>110601</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="16">
         <v>110602</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>110603</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="16">
         <v>110604</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>110607</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>110701</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>110702</v>
       </c>
@@ -7226,7 +7226,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>110703</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>110704</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>110801</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>110802</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>110803</v>
       </c>
@@ -7296,7 +7296,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>110804</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>110805</v>
       </c>
@@ -7324,7 +7324,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>110806</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>110807</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <v>110808</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>110809</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="18">
         <v>110810</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="16">
         <v>120901</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>120902</v>
       </c>
@@ -7422,7 +7422,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>120903</v>
       </c>
@@ -7436,7 +7436,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>120904</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>120905</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>120906</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>120907</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>120908</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>120909</v>
       </c>
@@ -7520,7 +7520,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
         <v>120910</v>
       </c>
@@ -7534,7 +7534,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <v>120912</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
         <v>120915</v>
       </c>
@@ -7562,7 +7562,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
         <v>120916</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
         <v>120917</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
         <v>120918</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
         <v>120919</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
         <v>121001</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
         <v>121002</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
         <v>121003</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
         <v>121004</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
         <v>121005</v>
       </c>
@@ -7688,7 +7688,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
         <v>121006</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
         <v>121007</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
         <v>121008</v>
       </c>
@@ -7730,7 +7730,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
         <v>121009</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
         <v>121010</v>
       </c>
@@ -7758,7 +7758,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
         <v>121011</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
         <v>121101</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
         <v>121102</v>
       </c>
@@ -7800,7 +7800,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="16">
         <v>121103</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
         <v>121104</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="16">
         <v>121105</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
         <v>121106</v>
       </c>
@@ -7856,7 +7856,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="16">
         <v>121107</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="16">
         <v>121111</v>
       </c>
@@ -7884,7 +7884,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
         <v>121112</v>
       </c>
@@ -7898,7 +7898,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="16">
         <v>121113</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <v>121114</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="16">
         <v>121115</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
         <v>121116</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="16">
         <v>121117</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
         <v>121201</v>
       </c>
@@ -7982,7 +7982,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="18">
         <v>121202</v>
       </c>
@@ -7996,7 +7996,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="16">
         <v>121301</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <v>121302</v>
       </c>
@@ -8024,7 +8024,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
         <v>121303</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <v>121304</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="16">
         <v>121305</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <v>121306</v>
       </c>
@@ -8080,7 +8080,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
         <v>121307</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <v>121309</v>
       </c>
@@ -8108,7 +8108,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
         <v>121310</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <v>121311</v>
       </c>
@@ -8136,7 +8136,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
         <v>121317</v>
       </c>
@@ -8150,7 +8150,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <v>121320</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
         <v>121321</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <v>121328</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
         <v>121329</v>
       </c>
@@ -8206,7 +8206,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <v>121330</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
         <v>121332</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <v>121333</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
         <v>121401</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <v>121402</v>
       </c>
@@ -8276,7 +8276,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
         <v>121403</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <v>121404</v>
       </c>
@@ -8304,7 +8304,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
         <v>121405</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <v>131501</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
         <v>131502</v>
       </c>
@@ -8346,7 +8346,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <v>131503</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
         <v>131504</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <v>131505</v>
       </c>
@@ -8388,7 +8388,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
         <v>131506</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
         <v>131507</v>
       </c>
@@ -8416,7 +8416,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
         <v>131508</v>
       </c>
@@ -8430,7 +8430,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
         <v>131509</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
         <v>131511</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
         <v>131515</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
         <v>131519</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
         <v>131524</v>
       </c>
@@ -8500,7 +8500,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
         <v>131525</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
         <v>131526</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
         <v>131527</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <v>131528</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <v>131529</v>
       </c>
@@ -8570,7 +8570,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <v>131531</v>
       </c>
@@ -8584,7 +8584,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
         <v>131534</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
         <v>131536</v>
       </c>
@@ -8612,7 +8612,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="8">
         <v>131601</v>
       </c>
@@ -8626,7 +8626,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>131602</v>
       </c>
@@ -8640,7 +8640,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>141801</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="8">
         <v>141802</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="8">
         <v>141803</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="8">
         <v>141804</v>
       </c>
@@ -8696,7 +8696,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="8">
         <v>141806</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="8">
         <v>141807</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="8">
         <v>141808</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="8">
         <v>141809</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="8">
         <v>141810</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="8">
         <v>141811</v>
       </c>
@@ -8780,7 +8780,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="8">
         <v>141812</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="8">
         <v>141901</v>
       </c>
@@ -8808,7 +8808,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="8">
         <v>141902</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="8">
         <v>141903</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="8">
         <v>141904</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="8">
         <v>141905</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="8">
         <v>141906</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="8">
         <v>141907</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="8">
         <v>141908</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="8">
         <v>142001</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="8">
         <v>142002</v>
       </c>
@@ -8934,7 +8934,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="8">
         <v>142101</v>
       </c>
@@ -8948,7 +8948,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="8">
         <v>142102</v>
       </c>
@@ -8962,7 +8962,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="8">
         <v>142103</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="8">
         <v>142104</v>
       </c>
@@ -8990,7 +8990,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="8">
         <v>142105</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="8">
         <v>142106</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="8">
         <v>142107</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
         <v>142108</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="8">
         <v>142109</v>
       </c>
@@ -9060,7 +9060,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="8">
         <v>142201</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="8">
         <v>142203</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="5">
         <v>152301</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="8">
         <v>152302</v>
       </c>
@@ -9116,7 +9116,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="8">
         <v>152304</v>
       </c>
@@ -9133,7 +9133,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="8">
         <v>152305</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="8">
         <v>152306</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="12">
         <v>152307</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="8">
         <v>152309</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="8">
         <v>152310</v>
       </c>
@@ -9206,7 +9206,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="8">
         <v>152312</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="8">
         <v>152315</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="8">
         <v>152316</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="8">
         <v>152318</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="8">
         <v>152322</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="8">
         <v>152401</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="8">
         <v>152404</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="8">
         <v>152501</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="8">
         <v>152506</v>
       </c>
@@ -9332,7 +9332,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="8">
         <v>152511</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="8">
         <v>152512</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="18">
         <v>152601</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="5">
         <v>162701</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="8">
         <v>162702</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="8">
         <v>162703</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="8">
         <v>162704</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="8">
         <v>162705</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="8">
         <v>162706</v>
       </c>
@@ -9458,7 +9458,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="8">
         <v>162707</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="8">
         <v>162708</v>
       </c>
@@ -9486,7 +9486,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="8">
         <v>162709</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="8">
         <v>162710</v>
       </c>
@@ -9514,7 +9514,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="8">
         <v>162711</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="8">
         <v>162713</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="12">
         <v>162716</v>
       </c>
@@ -9562,7 +9562,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="8">
         <v>162801</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="8">
         <v>162802</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="8">
         <v>162804</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="8">
         <v>162805</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="8">
         <v>162806</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="12">
         <v>162807</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="12">
         <v>162808</v>
       </c>
@@ -9669,7 +9669,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="8">
         <v>162901</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="8">
         <v>163001</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="8">
         <v>163101</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="8">
         <v>163102</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="8">
         <v>163103</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="8">
         <v>163104</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="8">
         <v>163105</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="8">
         <v>163106</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="8">
         <v>163107</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="8">
         <v>163108</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="8">
         <v>163201</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="8">
         <v>163203</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="8">
         <v>163206</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="8">
         <v>163301</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="8">
         <v>163303</v>
       </c>
@@ -9879,7 +9879,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="8">
         <v>163304</v>
       </c>
@@ -9893,7 +9893,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="18">
         <v>163406</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="261" spans="1:4" s="24" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:4" s="24" customFormat="1" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="21">
         <v>170202</v>
       </c>
@@ -9921,7 +9921,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="262" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="25">
         <v>170203</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="263" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="28">
         <v>170204</v>
       </c>
@@ -9949,7 +9949,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="264" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="28">
         <v>170205</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="265" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="28">
         <v>170206</v>
       </c>
@@ -9977,7 +9977,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="266" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="28">
         <v>170207</v>
       </c>
@@ -9991,7 +9991,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="267" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="28">
         <v>170208</v>
       </c>
@@ -10005,7 +10005,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="268" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="28">
         <v>170209</v>
       </c>
@@ -10019,7 +10019,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="269" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="28">
         <v>170210</v>
       </c>
@@ -10033,7 +10033,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="270" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="28">
         <v>170211</v>
       </c>
@@ -10047,7 +10047,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="271" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="28">
         <v>170212</v>
       </c>
@@ -10061,7 +10061,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="272" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="28">
         <v>170213</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="273" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="28">
         <v>170214</v>
       </c>
@@ -10089,7 +10089,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="274" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="28">
         <v>170215</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="275" spans="1:5" s="24" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:5" s="24" customFormat="1" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="31">
         <v>170216</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="34">
         <v>177777</v>
       </c>
@@ -10134,7 +10134,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="36">
         <v>180001</v>
       </c>
@@ -10148,7 +10148,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="5">
         <v>90001</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="8">
         <v>90002</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="8">
         <v>90003</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="8">
         <v>90004</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="8">
         <v>90005</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="8">
         <v>90006</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="8">
         <v>90007</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="8">
         <v>90008</v>
       </c>
@@ -10260,7 +10260,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="8">
         <v>90009</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="8">
         <v>90010</v>
       </c>
@@ -10288,7 +10288,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="8">
         <v>90011</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="8">
         <v>90012</v>
       </c>
@@ -10316,7 +10316,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="8">
         <v>90013</v>
       </c>
@@ -10330,7 +10330,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="8">
         <v>90014</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="8">
         <v>90015</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="8">
         <v>90016</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="8">
         <v>90017</v>
       </c>
@@ -10386,7 +10386,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="8">
         <v>90018</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="8">
         <v>90019</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="8">
         <v>90020</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="8">
         <v>90021</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="8">
         <v>90022</v>
       </c>
@@ -10456,7 +10456,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="8">
         <v>90023</v>
       </c>
@@ -10470,7 +10470,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="8">
         <v>90024</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="8">
         <v>90025</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="8">
         <v>90026</v>
       </c>
@@ -10512,7 +10512,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="8">
         <v>90027</v>
       </c>
@@ -10526,7 +10526,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="8">
         <v>90028</v>
       </c>
@@ -10540,7 +10540,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="8">
         <v>90029</v>
       </c>
@@ -10554,7 +10554,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="8">
         <v>90030</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="8">
         <v>90031</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="8">
         <v>90032</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="8">
         <v>90033</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="8">
         <v>90034</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="8">
         <v>90035</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="8">
         <v>90036</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="8">
         <v>90037</v>
       </c>
@@ -10666,7 +10666,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="8">
         <v>90038</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="8">
         <v>90039</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="8">
         <v>90040</v>
       </c>
@@ -10708,7 +10708,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="72">
         <v>999999</v>
       </c>
@@ -10739,17 +10739,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E204"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="41" customWidth="1"/>
+    <col min="1" max="1" width="11.2109375" style="41" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="42" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="68" customWidth="1"/>
-    <col min="5" max="5" width="34.125" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" style="41" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="89" t="s">
         <v>1</v>
       </c>
@@ -10772,7 +10772,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="46">
         <v>210101</v>
       </c>
@@ -10786,7 +10786,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="48">
         <v>210102</v>
       </c>
@@ -10800,7 +10800,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="48">
         <v>210103</v>
       </c>
@@ -10814,7 +10814,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="48">
         <v>210104</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="48">
         <v>210105</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="48">
         <v>210106</v>
       </c>
@@ -10856,7 +10856,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="48">
         <v>210107</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="48">
         <v>210108</v>
       </c>
@@ -10884,7 +10884,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="48">
         <v>210109</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="48">
         <v>210110</v>
       </c>
@@ -10912,7 +10912,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="48">
         <v>210112</v>
       </c>
@@ -10926,7 +10926,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="48">
         <v>210113</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="48">
         <v>210114</v>
       </c>
@@ -10954,7 +10954,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="48">
         <v>210115</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="48">
         <v>210116</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="48">
         <v>210117</v>
       </c>
@@ -10996,7 +10996,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="48">
         <v>210118</v>
       </c>
@@ -11010,7 +11010,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="48">
         <v>210119</v>
       </c>
@@ -11024,7 +11024,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="48">
         <v>210120</v>
       </c>
@@ -11041,7 +11041,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="50">
         <v>210121</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="48">
         <v>210123</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="52">
         <v>210124</v>
       </c>
@@ -11086,7 +11086,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="48">
         <v>210125</v>
       </c>
@@ -11100,7 +11100,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="48">
         <v>210201</v>
       </c>
@@ -11114,7 +11114,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="48">
         <v>210202</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="48">
         <v>210204</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="48">
         <v>210301</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="48">
         <v>210401</v>
       </c>
@@ -11170,7 +11170,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="48">
         <v>210402</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="48">
         <v>210403</v>
       </c>
@@ -11198,7 +11198,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="48">
         <v>210501</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="48">
         <v>210502</v>
       </c>
@@ -11226,7 +11226,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="48">
         <v>210503</v>
       </c>
@@ -11240,7 +11240,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="48">
         <v>210504</v>
       </c>
@@ -11254,7 +11254,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="48">
         <v>210505</v>
       </c>
@@ -11268,7 +11268,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="48">
         <v>210506</v>
       </c>
@@ -11282,7 +11282,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="48">
         <v>210601</v>
       </c>
@@ -11296,7 +11296,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="48">
         <v>210602</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="48">
         <v>210603</v>
       </c>
@@ -11324,7 +11324,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="48">
         <v>210701</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="48">
         <v>210702</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="52">
         <v>210801</v>
       </c>
@@ -11366,7 +11366,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="48">
         <v>210802</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="48">
         <v>210803</v>
       </c>
@@ -11394,7 +11394,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="54">
         <v>210804</v>
       </c>
@@ -11408,7 +11408,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="52">
         <v>220901</v>
       </c>
@@ -11422,7 +11422,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="48">
         <v>220902</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="48">
         <v>220903</v>
       </c>
@@ -11450,7 +11450,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="48">
         <v>220904</v>
       </c>
@@ -11464,7 +11464,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="48">
         <v>220905</v>
       </c>
@@ -11478,7 +11478,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="48">
         <v>220906</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="48">
         <v>220907</v>
       </c>
@@ -11506,7 +11506,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="48">
         <v>220908</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="48">
         <v>220909</v>
       </c>
@@ -11534,7 +11534,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="48">
         <v>220910</v>
       </c>
@@ -11548,7 +11548,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="48">
         <v>220911</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="48">
         <v>221001</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="48">
         <v>221002</v>
       </c>
@@ -11590,7 +11590,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="48">
         <v>221003</v>
       </c>
@@ -11604,7 +11604,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="48">
         <v>221101</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="48">
         <v>221102</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="50">
         <v>221103</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="48">
         <v>221104</v>
       </c>
@@ -11666,7 +11666,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="48">
         <v>221105</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="48">
         <v>221106</v>
       </c>
@@ -11694,7 +11694,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="48">
         <v>221107</v>
       </c>
@@ -11708,7 +11708,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="48">
         <v>221108</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="48">
         <v>221109</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="52">
         <v>221201</v>
       </c>
@@ -11750,7 +11750,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="54">
         <v>221202</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="52">
         <v>231301</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="48">
         <v>231302</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="48">
         <v>231303</v>
       </c>
@@ -11806,7 +11806,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="48">
         <v>231304</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="48">
         <v>231307</v>
       </c>
@@ -11834,7 +11834,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="48">
         <v>231308</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="48">
         <v>231309</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="48">
         <v>231401</v>
       </c>
@@ -11876,7 +11876,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="48">
         <v>231501</v>
       </c>
@@ -11890,7 +11890,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="48">
         <v>231502</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="48">
         <v>231504</v>
       </c>
@@ -11918,7 +11918,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="48">
         <v>231505</v>
       </c>
@@ -11932,7 +11932,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="48">
         <v>231506</v>
       </c>
@@ -11946,7 +11946,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="48">
         <v>231507</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="48">
         <v>231509</v>
       </c>
@@ -11974,7 +11974,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="48">
         <v>231510</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="48">
         <v>231511</v>
       </c>
@@ -12002,7 +12002,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="48">
         <v>231513</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="48">
         <v>231516</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="48">
         <v>231517</v>
       </c>
@@ -12044,7 +12044,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="48">
         <v>231518</v>
       </c>
@@ -12058,7 +12058,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="48">
         <v>231519</v>
       </c>
@@ -12072,7 +12072,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="54">
         <v>231601</v>
       </c>
@@ -12086,7 +12086,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="52">
         <v>241801</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="48">
         <v>241802</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="48">
         <v>241804</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="48">
         <v>241901</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="48">
         <v>241903</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="48">
         <v>242001</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="48">
         <v>242101</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="48">
         <v>242102</v>
       </c>
@@ -12198,7 +12198,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="48">
         <v>242103</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="48">
         <v>242104</v>
       </c>
@@ -12226,7 +12226,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="48">
         <v>242105</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="48">
         <v>242201</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="54">
         <v>242202</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="52">
         <v>252301</v>
       </c>
@@ -12282,7 +12282,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="48">
         <v>252302</v>
       </c>
@@ -12296,7 +12296,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="48">
         <v>252303</v>
       </c>
@@ -12310,7 +12310,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="48">
         <v>252304</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="48">
         <v>252305</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="48">
         <v>252306</v>
       </c>
@@ -12352,7 +12352,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="48">
         <v>252307</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="48">
         <v>252308</v>
       </c>
@@ -12380,7 +12380,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="48">
         <v>252309</v>
       </c>
@@ -12394,7 +12394,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="48">
         <v>252310</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="48">
         <v>252311</v>
       </c>
@@ -12422,7 +12422,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="48">
         <v>252402</v>
       </c>
@@ -12436,7 +12436,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="48">
         <v>252501</v>
       </c>
@@ -12450,7 +12450,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="48">
         <v>252503</v>
       </c>
@@ -12464,7 +12464,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="48">
         <v>252505</v>
       </c>
@@ -12478,7 +12478,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="56">
         <v>252601</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="52">
         <v>262701</v>
       </c>
@@ -12509,7 +12509,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="48">
         <v>262702</v>
       </c>
@@ -12526,7 +12526,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="50">
         <v>262703</v>
       </c>
@@ -12543,7 +12543,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="50">
         <v>262704</v>
       </c>
@@ -12560,7 +12560,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="50">
         <v>262705</v>
       </c>
@@ -12577,7 +12577,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="48">
         <v>262706</v>
       </c>
@@ -12591,7 +12591,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="50">
         <v>262707</v>
       </c>
@@ -12608,7 +12608,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="48">
         <v>262709</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="48">
         <v>262801</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="48">
         <v>262901</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="48">
         <v>263001</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="48">
         <v>263003</v>
       </c>
@@ -12678,7 +12678,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="48">
         <v>263004</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="48">
         <v>263101</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="48">
         <v>263103</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="48">
         <v>263104</v>
       </c>
@@ -12734,7 +12734,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="48">
         <v>263201</v>
       </c>
@@ -12748,7 +12748,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="48">
         <v>263301</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="48">
         <v>263401</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="58">
         <v>263404</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="44">
         <v>270001</v>
       </c>
@@ -12804,7 +12804,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="44">
         <v>270202</v>
       </c>
@@ -12818,7 +12818,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="46">
         <v>270203</v>
       </c>
@@ -12832,7 +12832,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="48">
         <v>270204</v>
       </c>
@@ -12846,7 +12846,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="48">
         <v>270205</v>
       </c>
@@ -12860,7 +12860,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="48">
         <v>270206</v>
       </c>
@@ -12874,7 +12874,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="48">
         <v>270207</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="48">
         <v>270208</v>
       </c>
@@ -12902,7 +12902,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="48">
         <v>270209</v>
       </c>
@@ -12916,7 +12916,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="48">
         <v>270210</v>
       </c>
@@ -12930,7 +12930,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="48">
         <v>270211</v>
       </c>
@@ -12944,7 +12944,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="48">
         <v>270212</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="48">
         <v>270213</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="48">
         <v>270214</v>
       </c>
@@ -12986,7 +12986,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="48">
         <v>270215</v>
       </c>
@@ -13000,7 +13000,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="60">
         <v>270216</v>
       </c>
@@ -13017,7 +13017,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="13.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="61">
         <v>280001</v>
       </c>
@@ -13031,7 +13031,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="162" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="63">
         <v>90001</v>
       </c>
@@ -13045,7 +13045,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="163" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="66">
         <v>90002</v>
       </c>
@@ -13059,7 +13059,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="164" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="66">
         <v>90003</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="165" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="66">
         <v>90004</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="166" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="66">
         <v>90005</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="167" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="66">
         <v>90006</v>
       </c>
@@ -13115,7 +13115,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="168" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="66">
         <v>90007</v>
       </c>
@@ -13129,7 +13129,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="169" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="66">
         <v>90008</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="170" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="66">
         <v>90009</v>
       </c>
@@ -13157,7 +13157,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="171" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="66">
         <v>90010</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="172" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="66">
         <v>90011</v>
       </c>
@@ -13185,7 +13185,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="173" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="66">
         <v>90012</v>
       </c>
@@ -13199,7 +13199,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="174" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="66">
         <v>90013</v>
       </c>
@@ -13213,7 +13213,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="175" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="66">
         <v>90014</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="176" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="66">
         <v>90015</v>
       </c>
@@ -13241,7 +13241,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="177" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="66">
         <v>90016</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="178" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="66">
         <v>90017</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="179" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="66">
         <v>90018</v>
       </c>
@@ -13283,7 +13283,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="180" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="66">
         <v>90019</v>
       </c>
@@ -13297,7 +13297,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="181" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="66">
         <v>90020</v>
       </c>
@@ -13311,7 +13311,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="182" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="66">
         <v>90021</v>
       </c>
@@ -13325,7 +13325,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="183" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="66">
         <v>90022</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="66">
         <v>90023</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="185" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="66">
         <v>90024</v>
       </c>
@@ -13367,7 +13367,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="186" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="66">
         <v>90025</v>
       </c>
@@ -13381,7 +13381,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="187" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="66">
         <v>90026</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="188" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="66">
         <v>90027</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="189" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="66">
         <v>90028</v>
       </c>
@@ -13423,7 +13423,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="190" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="66">
         <v>90029</v>
       </c>
@@ -13437,7 +13437,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="191" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="66">
         <v>90030</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="192" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="66">
         <v>90031</v>
       </c>
@@ -13465,7 +13465,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="193" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="66">
         <v>90032</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="194" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="66">
         <v>90033</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="195" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="66">
         <v>90034</v>
       </c>
@@ -13507,7 +13507,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="196" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="66">
         <v>90035</v>
       </c>
@@ -13521,7 +13521,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="197" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="66">
         <v>90036</v>
       </c>
@@ -13535,7 +13535,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="198" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="66">
         <v>90037</v>
       </c>
@@ -13549,7 +13549,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="199" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="66">
         <v>90038</v>
       </c>
@@ -13563,7 +13563,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="200" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="66">
         <v>90039</v>
       </c>
@@ -13577,7 +13577,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="201" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:4" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="66">
         <v>90040</v>
       </c>
@@ -13591,7 +13591,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="58">
         <v>999999</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="42"/>
     </row>
   </sheetData>
